--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>ODP</t>
   </si>
@@ -656,414 +656,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44828</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44737</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44555</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44464</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44373</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44282</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44191</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2009000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1908000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2108000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2106000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2172000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2034000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2178000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2042000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2179000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2070000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2174000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2085000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2347000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4440000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2725000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2508000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2782000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2588000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2769000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2670000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2887000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2628000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1410000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1535000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1493000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1627000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1660000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1686000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1603000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1694000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1610000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1675000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4955000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3511000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3426000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1800000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3486000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2096000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1937000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2115000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2003000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2128000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2068000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2201000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2032000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E10" s="3">
         <v>474000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>415000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>481000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>446000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>486000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>431000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>484000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>432000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>504000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>547000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>954000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>629000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>571000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>667000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>585000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>641000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>602000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>686000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>596000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>667000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>654000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1096,8 +1108,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1188,8 +1201,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,100 +1296,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E14" s="3">
         <v>4000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>3000</v>
       </c>
       <c r="J14" s="3">
         <v>3000</v>
       </c>
       <c r="K14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L14" s="3">
         <v>16000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>18000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>38000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>20000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>34000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>242000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>28000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>17000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>27000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>85000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>74000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>14000</v>
       </c>
       <c r="Y14" s="3">
         <v>14000</v>
       </c>
       <c r="Z14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AA14" s="3">
         <v>17000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>35000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>22000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>21000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>20000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>48000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1464,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,192 +1520,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1918000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1862000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2013000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2051000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2088000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2006000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2102000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2011000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2075000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2040000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2105000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2065000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2245000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4568000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2645000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2434000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2674000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2603000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2745000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2661000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2782000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2580000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E18" s="3">
         <v>91000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>95000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>55000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>84000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>76000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>31000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>104000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>69000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>102000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-128000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>80000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>74000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>108000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>105000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>48000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>77000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>55000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>105000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>41000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>124000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>58000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,70 +1745,71 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="E20" s="3">
         <v>6000</v>
       </c>
       <c r="F20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>2000</v>
       </c>
       <c r="P20" s="3">
         <v>2000</v>
       </c>
       <c r="Q20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R20" s="3">
         <v>6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>7000</v>
       </c>
       <c r="U20" s="3">
         <v>7000</v>
       </c>
       <c r="V20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W20" s="3">
         <v>8000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>11000</v>
       </c>
       <c r="X20" s="3">
         <v>11000</v>
@@ -1785,120 +1818,126 @@
         <v>11000</v>
       </c>
       <c r="Z20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>7000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>8000</v>
       </c>
       <c r="AC20" s="3">
         <v>8000</v>
       </c>
       <c r="AD20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>10000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
         <v>125000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>81000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>129000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>89000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>122000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>66000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>113000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>73000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>128000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>78000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>126000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>68000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>150000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-25000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>133000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>145000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>167000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>45000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>81000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>70000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>160000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>110000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>131000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>107000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>150000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>88000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>174000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>104000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1912,269 +1951,278 @@
         <v>5000</v>
       </c>
       <c r="G22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H22" s="3">
         <v>6000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>28000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>23000</v>
       </c>
       <c r="V22" s="3">
         <v>23000</v>
       </c>
       <c r="W22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="X22" s="3">
         <v>30000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>31000</v>
       </c>
       <c r="Y22" s="3">
         <v>31000</v>
       </c>
       <c r="Z22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>29000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>13000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>17000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E23" s="3">
         <v>92000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>52000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>89000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>28000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>74000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>100000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>98000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-150000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>66000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>74000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>93000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-31000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>85000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>28000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>55000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>41000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>100000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>35000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>121000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>46000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>22000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-17000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>64000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-22000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>33000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>25000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>22000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>158000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>14000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>47000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,192 +2313,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E26" s="3">
         <v>70000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>72000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>36000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>67000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>55000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>31000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-128000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>45000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>55000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>60000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-24000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>60000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>33000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-117000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>98000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>21000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>74000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>55000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E27" s="3">
         <v>70000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>72000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>36000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>67000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>55000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>63000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-128000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>45000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>55000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>60000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-24000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>60000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>33000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-117000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>98000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>74000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>55000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2556,44 +2616,44 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-19000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>7000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-306000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>28000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-225000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-10000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-13000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>23000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-266000</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
@@ -2610,31 +2670,34 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>8000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>65000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>6000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>84000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>174000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,70 +2883,73 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6000</v>
+        <v>-4000</v>
       </c>
       <c r="E32" s="3">
         <v>-6000</v>
       </c>
       <c r="F32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-2000</v>
       </c>
       <c r="P32" s="3">
         <v>-2000</v>
       </c>
       <c r="Q32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="R32" s="3">
         <v>-6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-7000</v>
       </c>
       <c r="U32" s="3">
         <v>-7000</v>
       </c>
       <c r="V32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-11000</v>
       </c>
       <c r="X32" s="3">
         <v>-11000</v>
@@ -2889,120 +2958,126 @@
         <v>-11000</v>
       </c>
       <c r="Z32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AC32" s="3">
         <v>-8000</v>
       </c>
       <c r="AD32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E33" s="3">
         <v>70000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>72000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>55000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-274000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>101000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-205000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>53000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>57000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-394000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>45000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>55000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>60000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-24000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>60000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>41000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>86000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>27000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>158000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>229000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,197 +3168,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E35" s="3">
         <v>70000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>72000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>55000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-274000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>101000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-205000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>53000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>57000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-394000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>45000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>55000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>60000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-24000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>60000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>41000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>86000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>27000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>158000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>229000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44828</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44737</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44555</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44464</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44373</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44282</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44191</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,100 +3435,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E41" s="3">
         <v>384000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>335000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>343000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>403000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>473000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>417000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>557000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>514000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>753000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>691000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>753000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>729000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>743000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>762000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>842000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>698000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>588000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>444000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>604000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>658000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>925000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>747000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>737000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>622000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>788000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>763000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>744000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>763000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3534,376 +3623,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E43" s="3">
         <v>547000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>521000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>529000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>544000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>601000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>577000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>586000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>511000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>499000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>699000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>704000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>457000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>678000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>698000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>850000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1642000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1744000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1732000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1780000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>885000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>950000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>905000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>942000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>931000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>693000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>652000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>688000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>687000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E44" s="3">
         <v>782000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>836000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>793000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>828000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>890000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>968000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>866000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>859000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>841000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>957000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>929000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>916000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1000000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1005000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>929000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1032000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1025000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1113000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1034000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1065000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1023000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1122000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E45" s="3">
         <v>41000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>46000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>148000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>135000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>144000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>505000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>783000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>64000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>253000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>59000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>60000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>79000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>75000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>103000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>84000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>75000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>112000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>142000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>216000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>225000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>241000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>269000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>313000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>244000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1678000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1754000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1738000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1813000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1910000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2108000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2011000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2053000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2389000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2876000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2411000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2444000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2355000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2480000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2525000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2700000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3447000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3460000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3389000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3502000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2683000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3010000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2916000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3914,47 +4018,47 @@
         <v>1000</v>
       </c>
       <c r="F47" s="3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G47" s="3">
         <v>2000</v>
       </c>
       <c r="H47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I47" s="3">
         <v>3000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>17000</v>
       </c>
-      <c r="R47" s="3" t="s">
+      <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
       <c r="T47" s="3">
         <v>0</v>
       </c>
@@ -3965,221 +4069,230 @@
         <v>0</v>
       </c>
       <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
         <v>842000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>847000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>853000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>858000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>863000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>869000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>874000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>879000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>885000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1342000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1303000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1240000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1230000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1226000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1365000</v>
       </c>
       <c r="J48" s="3">
         <v>1365000</v>
       </c>
       <c r="K48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="L48" s="3">
         <v>1413000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1440000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1586000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1642000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1649000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1811000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1884000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2019000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2092000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2073000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2106000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2128000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>763000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>744000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>722000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>713000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>725000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>627000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>580000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>601000</v>
       </c>
       <c r="AF48" s="3">
         <v>601000</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>601000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>510000</v>
+        <v>448000</v>
       </c>
       <c r="E49" s="3">
         <v>510000</v>
       </c>
       <c r="F49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="G49" s="3">
         <v>511000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>510000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>511000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>514000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>516000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>518000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>519000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>916000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1034000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>451000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>965000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>956000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1319000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1332000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1333000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1345000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1331000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1336000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1342000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>395000</v>
       </c>
       <c r="AD49" s="3">
         <v>395000</v>
       </c>
       <c r="AE49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>396000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,100 +4478,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E52" s="3">
         <v>412000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>472000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>485000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>501000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>552000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>580000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>590000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>537000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>506000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>452000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>464000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1144000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>475000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>483000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>416000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>440000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>477000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>513000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>510000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>542000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>529000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>549000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>561000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>565000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>651000</v>
       </c>
       <c r="AD52" s="3">
         <v>651000</v>
       </c>
       <c r="AE52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>685000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,100 +4668,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3886000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3980000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3961000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4041000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4149000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4418000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4474000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4529000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4865000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5351000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5378000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5598000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5614000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5745000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5865000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6454000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7311000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7343000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7353000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7471000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6166000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6472000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6359000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,100 +4835,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E57" s="3">
         <v>818000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>864000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>903000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>821000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>853000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>917000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>975000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>950000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>863000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>979000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>959000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>857000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1038000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>991000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1006000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1026000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1037000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1089000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1098000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1110000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1085000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1066000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>969000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>892000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>889000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>873000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>835000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>893000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4810,456 +4943,471 @@
         <v>9000</v>
       </c>
       <c r="F58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G58" s="3">
         <v>12000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>16000</v>
       </c>
       <c r="H58" s="3">
         <v>16000</v>
       </c>
       <c r="I58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J58" s="3">
         <v>17000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>20000</v>
       </c>
       <c r="L58" s="3">
         <v>20000</v>
       </c>
       <c r="M58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N58" s="3">
         <v>22000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>23000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>30000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>104000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>841000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>842000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>837000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>841000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>95000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>92000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>97000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>93000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>96000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>28000</v>
       </c>
       <c r="AD58" s="3">
         <v>28000</v>
       </c>
       <c r="AE58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AF58" s="3">
         <v>29000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>929000</v>
+      </c>
+      <c r="E59" s="3">
         <v>933000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>909000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>930000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1022000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1024000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>969000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>973000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1295000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1298000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1099000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1147000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1556000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1228000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1114000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1235000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1227000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1277000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1255000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1294000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>980000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1051000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>957000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>952000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>926000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>983000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1693000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1760000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1782000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1845000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1859000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1893000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1903000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1966000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2265000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2181000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2100000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2129000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2093000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2287000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2135000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2345000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3094000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3156000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3181000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3233000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2185000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2228000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2120000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E61" s="3">
         <v>164000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>172000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>210000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>172000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>175000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>177000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>181000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>228000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>333000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>337000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>344000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>354000</v>
       </c>
       <c r="P61" s="3">
         <v>354000</v>
       </c>
       <c r="Q61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="R61" s="3">
         <v>642000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>548000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>575000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>593000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>618000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>632000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1444000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1646000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1668000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E62" s="3">
         <v>901000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>846000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>838000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>831000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>851000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>881000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>890000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>934000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>975000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1165000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1287000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1309000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1371000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1426000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1469000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1467000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1472000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1500000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>411000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>401000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>415000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>421000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>427000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>451000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>476000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>490000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>501000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,100 +5688,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2825000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2800000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2893000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2862000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2919000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2961000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3037000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3427000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3489000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3537000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3638000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3734000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3950000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4148000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4319000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5138000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5216000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5271000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5365000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4040000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4275000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4203000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6008,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5936,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,100 +6198,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-275000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-344000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-379000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-451000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-468000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-535000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-562000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-617000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-343000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-444000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-356000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-409000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-427000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-484000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-45000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-89000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-144000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-204000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-180000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-173000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-160000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-220000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,100 +6578,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1101000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1155000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1161000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1148000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1287000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1499000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1513000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1492000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1438000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1862000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1841000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1960000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1880000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1795000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1717000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2135000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2173000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2127000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2082000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2106000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2126000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2197000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2156000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,197 +6768,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44828</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44737</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44555</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44464</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44373</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44282</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44191</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E81" s="3">
         <v>70000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>72000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>55000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-274000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>101000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-205000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>53000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>57000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-394000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>45000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>55000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>60000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-24000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>60000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>41000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>86000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>27000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>158000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>229000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,8 +7000,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6812,34 +7010,34 @@
         <v>28000</v>
       </c>
       <c r="E83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F83" s="3">
         <v>29000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>34000</v>
       </c>
       <c r="J83" s="3">
         <v>34000</v>
       </c>
       <c r="K83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="L83" s="3">
         <v>36000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>43000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>46000</v>
       </c>
       <c r="O83" s="3">
         <v>46000</v>
@@ -6848,55 +7046,58 @@
         <v>46000</v>
       </c>
       <c r="Q83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R83" s="3">
         <v>97000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>49000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>50000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>52000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>53000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>50000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>44000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>47000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>51000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>43000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>37000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>39000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>40000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,100 +7568,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E89" s="3">
         <v>112000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>157000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>158000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>163000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-114000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>171000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>86000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>309000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>180000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>188000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>152000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>212000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-58000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>60000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>61000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>304000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>45000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>217000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>282000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>34000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>102000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>36000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,100 +7700,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-14000</v>
       </c>
       <c r="P91" s="3">
         <v>-14000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-40000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-45000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-46000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-66000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-37000</v>
       </c>
       <c r="Z91" s="3">
         <v>-37000</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>13000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>31000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,100 +7983,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>77000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>53000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-33000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>762000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>776000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>23000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-29000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-61000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-52000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-68000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-76000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>23000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7928,28 +8161,28 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>-13000</v>
       </c>
       <c r="S96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="T96" s="3">
         <v>-14000</v>
       </c>
       <c r="U96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-13000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-14000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-14000</v>
       </c>
       <c r="Y96" s="3">
         <v>-14000</v>
@@ -7961,7 +8194,7 @@
         <v>-14000</v>
       </c>
       <c r="AB96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AC96" s="3">
         <v>-13000</v>
@@ -7975,8 +8208,11 @@
       <c r="AF96" s="3">
         <v>-13000</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-13000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,280 +8493,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-43000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-78000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-185000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-204000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-77000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-64000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-291000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-85000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-53000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-30000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-316000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-872000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-808000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-67000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-38000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-64000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-255000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-52000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>672000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-6000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>2000</v>
       </c>
       <c r="V101" s="3">
         <v>2000</v>
       </c>
       <c r="W101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X101" s="3">
         <v>-5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>3000</v>
       </c>
       <c r="AC101" s="3">
         <v>3000</v>
       </c>
       <c r="AD101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>50000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-59000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-70000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>57000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-140000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-216000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>62000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-62000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>64000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>144000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>110000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>144000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-160000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-54000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-267000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>177000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>138000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-175000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>ODP</t>
   </si>
@@ -656,426 +656,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44828</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44737</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44646</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44555</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44464</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44373</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44282</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44191</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1871000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1806000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2009000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1908000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2108000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2106000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2172000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2034000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2178000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2042000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2179000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2070000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2174000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2085000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2347000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4440000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2725000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2508000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2782000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2588000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2769000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2670000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2887000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2628000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1461000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1410000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1535000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1493000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1627000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1660000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1686000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1603000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1694000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1610000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1675000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4955000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3511000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3426000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1800000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3486000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2096000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1937000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2115000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2003000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2128000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2068000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2201000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2032000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E10" s="3">
         <v>396000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>474000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>415000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>481000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>446000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>486000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>431000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>484000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>432000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>504000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>547000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>954000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>629000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>571000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>667000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>585000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>641000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>602000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>686000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>596000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>667000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>654000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,8 +1122,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1204,8 +1218,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,103 +1316,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E14" s="3">
         <v>74000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3000</v>
       </c>
       <c r="K14" s="3">
         <v>3000</v>
       </c>
       <c r="L14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M14" s="3">
         <v>16000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>38000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>20000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>34000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>242000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>28000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>17000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>27000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>85000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>43000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>74000</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>14000</v>
       </c>
       <c r="Z14" s="3">
         <v>14000</v>
       </c>
       <c r="AA14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AB14" s="3">
         <v>17000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>35000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>22000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>21000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>20000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>48000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1547,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1837000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1918000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1862000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2013000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2051000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2088000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2006000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2102000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2011000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2075000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2040000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2105000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2065000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2245000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4568000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2645000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2434000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2674000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2603000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2745000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2661000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2782000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>91000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>95000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>55000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>84000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>76000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>31000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>104000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>69000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>102000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-128000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>80000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>74000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>108000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>105000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>48000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>77000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>55000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>105000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>41000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>124000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>58000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,73 +1779,74 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>6000</v>
       </c>
       <c r="F20" s="3">
         <v>6000</v>
       </c>
       <c r="G20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H20" s="3">
         <v>4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2000</v>
       </c>
       <c r="Q20" s="3">
         <v>2000</v>
       </c>
       <c r="R20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S20" s="3">
         <v>6000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>21000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>7000</v>
       </c>
       <c r="V20" s="3">
         <v>7000</v>
       </c>
       <c r="W20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X20" s="3">
         <v>8000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>11000</v>
       </c>
       <c r="Y20" s="3">
         <v>11000</v>
@@ -1821,128 +1855,134 @@
         <v>11000</v>
       </c>
       <c r="AA20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>7000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>8000</v>
       </c>
       <c r="AD20" s="3">
         <v>8000</v>
       </c>
       <c r="AE20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>10000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>125000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>81000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>129000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>89000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>122000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>113000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>73000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>128000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>78000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>126000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>68000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>150000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-25000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>133000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>145000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>167000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>81000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>70000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>160000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>110000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>131000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>107000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>150000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>88000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>174000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>104000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="E22" s="3">
         <v>5000</v>
@@ -1954,275 +1994,284 @@
         <v>5000</v>
       </c>
       <c r="H22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I22" s="3">
         <v>6000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>23000</v>
       </c>
       <c r="W22" s="3">
         <v>23000</v>
       </c>
       <c r="X22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>30000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>31000</v>
       </c>
       <c r="Z22" s="3">
         <v>31000</v>
       </c>
       <c r="AA22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>29000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>13000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>14000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>13000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>17000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>92000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>52000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>89000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>28000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>74000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>100000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>73000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>98000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-150000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>66000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>74000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>93000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-31000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>85000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>28000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>55000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>41000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>100000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>35000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>121000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>46000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>64000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-22000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>25000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>22000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>158000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>47000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2365,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>70000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>67000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>55000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>63000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>34000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-128000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>45000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>55000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>60000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-24000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>60000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>33000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>98000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>21000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>74000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>55000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>70000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>72000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>67000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>55000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>63000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>34000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-128000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>45000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>55000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>60000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-24000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>60000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>33000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>98000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>21000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>74000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>55000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2619,44 +2680,44 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-19000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>7000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-306000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>28000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-225000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-10000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>23000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-266000</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2673,31 +2734,34 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>8000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>65000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>6000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>84000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>174000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,73 +2953,76 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-6000</v>
       </c>
       <c r="F32" s="3">
         <v>-6000</v>
       </c>
       <c r="G32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q32" s="3">
         <v>-2000</v>
       </c>
       <c r="R32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S32" s="3">
         <v>-6000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-7000</v>
       </c>
       <c r="V32" s="3">
         <v>-7000</v>
       </c>
       <c r="W32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="X32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-11000</v>
       </c>
       <c r="Y32" s="3">
         <v>-11000</v>
@@ -2961,123 +3031,129 @@
         <v>-11000</v>
       </c>
       <c r="AA32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AD32" s="3">
         <v>-8000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>70000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>72000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>67000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>55000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-274000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>101000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-205000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>53000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>57000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-394000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>45000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>55000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>60000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-24000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>60000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>41000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>86000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>27000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>158000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>229000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3247,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>70000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>72000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>67000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>55000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-274000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>101000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-205000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>53000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>57000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-394000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>45000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>55000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>60000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-24000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>60000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>41000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>86000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>27000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>158000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>229000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44828</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44737</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44646</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44555</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44464</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44373</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44282</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44191</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,103 +3522,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E41" s="3">
         <v>392000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>384000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>335000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>343000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>403000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>473000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>417000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>557000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>514000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>753000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>691000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>753000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>729000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>743000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>762000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>842000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>698000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>588000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>444000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>604000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>658000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>925000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>747000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>737000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>622000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>788000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>763000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>744000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>763000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3626,388 +3716,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E43" s="3">
         <v>491000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>547000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>521000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>529000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>544000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>601000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>577000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>586000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>511000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>499000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>699000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>704000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>457000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>678000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>698000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>850000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1642000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1744000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1732000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1780000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>885000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>950000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>905000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>942000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>931000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>693000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>652000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>688000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>687000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>733000</v>
+      </c>
+      <c r="E44" s="3">
         <v>765000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>782000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>836000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>793000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>828000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>890000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>968000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>866000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>859000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>841000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>957000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>929000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>916000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1000000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1005000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>929000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1032000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1025000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1113000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1034000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1065000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1023000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1122000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E45" s="3">
         <v>30000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>148000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>135000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>144000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>505000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>783000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>64000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>58000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>253000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>59000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>60000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>79000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>75000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>103000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>84000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>75000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>112000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>142000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>216000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>225000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>241000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>269000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>313000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>244000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1524000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1678000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1754000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1738000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1813000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1910000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2108000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2011000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2053000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2389000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2876000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2411000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2444000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2355000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2480000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2525000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2700000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3447000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3460000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3389000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3502000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2683000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3010000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2916000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4021,47 +4126,47 @@
         <v>1000</v>
       </c>
       <c r="G47" s="3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H47" s="3">
         <v>2000</v>
       </c>
       <c r="I47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J47" s="3">
         <v>3000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>17000</v>
       </c>
-      <c r="S47" s="3" t="s">
+      <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
       <c r="U47" s="3">
         <v>0</v>
       </c>
@@ -4072,227 +4177,236 @@
         <v>0</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>842000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>847000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>853000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>858000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>863000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>869000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>874000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>879000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>885000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1342000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1303000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1240000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1230000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1226000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1365000</v>
       </c>
       <c r="K48" s="3">
         <v>1365000</v>
       </c>
       <c r="L48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="M48" s="3">
         <v>1413000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1440000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1586000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1642000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1649000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1811000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1884000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2019000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2092000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2073000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2106000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2128000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>763000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>744000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>722000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>713000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>725000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>627000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>580000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>601000</v>
       </c>
       <c r="AG48" s="3">
         <v>601000</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>601000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E49" s="3">
         <v>448000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>510000</v>
       </c>
       <c r="F49" s="3">
         <v>510000</v>
       </c>
       <c r="G49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="H49" s="3">
         <v>511000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>510000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>511000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>514000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>516000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>518000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>519000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>916000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1034000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>451000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>965000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>956000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1319000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1332000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1333000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1345000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1331000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1336000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1342000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>395000</v>
       </c>
       <c r="AE49" s="3">
         <v>395000</v>
       </c>
       <c r="AF49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>396000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,103 +4598,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E52" s="3">
         <v>417000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>412000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>472000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>485000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>501000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>552000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>580000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>590000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>537000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>506000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>452000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>464000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1144000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>475000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>483000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>416000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>440000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>477000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>513000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>510000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>542000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>529000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>549000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>561000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>565000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>651000</v>
       </c>
       <c r="AE52" s="3">
         <v>651000</v>
       </c>
       <c r="AF52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AG52" s="3">
         <v>685000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,103 +4794,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3735000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3886000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3980000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3961000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4041000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4149000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4418000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4474000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4529000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4865000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5351000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5378000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5598000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5614000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5745000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5865000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6454000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7311000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7343000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7353000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7471000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6166000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6472000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6359000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,8 +4966,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4845,99 +4976,102 @@
         <v>755000</v>
       </c>
       <c r="E57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="F57" s="3">
         <v>818000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>864000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>903000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>821000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>853000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>917000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>975000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>950000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>863000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>979000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>959000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>857000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1038000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>991000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1006000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1026000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1037000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1089000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1098000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1110000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1085000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1066000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>969000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>892000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>889000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>873000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>835000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>893000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="E58" s="3">
         <v>9000</v>
@@ -4946,373 +5080,385 @@
         <v>9000</v>
       </c>
       <c r="G58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="H58" s="3">
         <v>12000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>16000</v>
       </c>
       <c r="I58" s="3">
         <v>16000</v>
       </c>
       <c r="J58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K58" s="3">
         <v>17000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>20000</v>
       </c>
       <c r="M58" s="3">
         <v>20000</v>
       </c>
       <c r="N58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O58" s="3">
         <v>22000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>23000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>21000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>30000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>104000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>841000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>842000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>837000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>841000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>95000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>92000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>97000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>93000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>96000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>28000</v>
       </c>
       <c r="AE58" s="3">
         <v>28000</v>
       </c>
       <c r="AF58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AG58" s="3">
         <v>29000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>859000</v>
+      </c>
+      <c r="E59" s="3">
         <v>929000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>933000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>909000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>930000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1022000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1024000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>969000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>973000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1295000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1298000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1099000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1147000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1556000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1228000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1114000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1235000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1227000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1277000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1255000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1294000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>980000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1051000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>957000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>952000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>926000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>983000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1693000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1760000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1782000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1845000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1859000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1893000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1903000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1966000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2265000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2181000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2100000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2129000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2093000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2287000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2135000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2345000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3094000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3156000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3181000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3233000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2185000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2228000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2120000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E61" s="3">
         <v>165000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>164000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>172000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>210000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>172000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>175000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>177000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>181000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>228000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>333000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>337000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>344000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>354000</v>
       </c>
       <c r="Q61" s="3">
         <v>354000</v>
       </c>
       <c r="R61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="S61" s="3">
         <v>642000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>548000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>575000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>593000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>618000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>632000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1444000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1646000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1668000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5320,94 +5466,97 @@
         <v>927000</v>
       </c>
       <c r="E62" s="3">
+        <v>927000</v>
+      </c>
+      <c r="F62" s="3">
         <v>901000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>846000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>838000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>831000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>851000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>881000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>890000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>934000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>975000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1100000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1165000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1287000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1309000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1371000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1426000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1469000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1467000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1472000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1500000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>411000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>401000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>415000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>421000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>427000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>451000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>476000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>490000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>501000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,103 +5846,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2666000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2785000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2825000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2800000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2893000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2862000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2919000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2961000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3037000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3427000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3489000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3537000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3638000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3734000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3950000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4148000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4319000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5138000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5216000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5271000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5365000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4040000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4275000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,103 +6372,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-297000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-312000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-275000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-344000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-379000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-451000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-468000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-535000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-562000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-617000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-343000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-444000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-356000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-409000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-427000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-484000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-45000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-89000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-144000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-204000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-180000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-173000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-160000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-220000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,103 +6764,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1069000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1101000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1155000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1161000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1148000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1287000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1499000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1513000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1492000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1438000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1862000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1841000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1960000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1880000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1795000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1717000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2135000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2173000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2127000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2082000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2106000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2126000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2197000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6960,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44828</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44737</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44646</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44555</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44464</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44373</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44282</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44191</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>70000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>72000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>67000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>55000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-274000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>101000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-205000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>53000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>57000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-394000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>45000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>55000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>60000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-24000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>60000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>41000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>86000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>27000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>158000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>229000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,46 +7199,47 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="E83" s="3">
         <v>28000</v>
       </c>
       <c r="F83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="G83" s="3">
         <v>29000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>34000</v>
       </c>
       <c r="K83" s="3">
         <v>34000</v>
       </c>
       <c r="L83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="M83" s="3">
         <v>36000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>46000</v>
       </c>
       <c r="P83" s="3">
         <v>46000</v>
@@ -7049,55 +7248,58 @@
         <v>46000</v>
       </c>
       <c r="R83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="S83" s="3">
         <v>97000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>49000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>50000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>52000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>53000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>49000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>50000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>44000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>47000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>51000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>43000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>37000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>39000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>40000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,103 +7785,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E89" s="3">
         <v>70000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>112000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>157000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>158000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>163000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-114000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>171000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>86000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>309000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>180000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>188000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>152000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>212000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-58000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>60000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>61000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>304000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>45000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>217000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>40000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>282000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>34000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>102000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>36000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,103 +7921,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-14000</v>
       </c>
       <c r="Q91" s="3">
         <v>-14000</v>
       </c>
       <c r="R91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-40000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-32000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-37000</v>
       </c>
       <c r="AA91" s="3">
         <v>-37000</v>
       </c>
       <c r="AB91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>13000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>31000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,103 +8213,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>77000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>53000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-33000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>762000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>776000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>23000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-29000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-61000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-52000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-68000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>23000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,8 +8349,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8164,28 +8398,28 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>-13000</v>
       </c>
       <c r="T96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="U96" s="3">
         <v>-14000</v>
       </c>
       <c r="V96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-13000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-14000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-14000</v>
       </c>
       <c r="Z96" s="3">
         <v>-14000</v>
@@ -8197,7 +8431,7 @@
         <v>-14000</v>
       </c>
       <c r="AC96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AD96" s="3">
         <v>-13000</v>
@@ -8211,8 +8445,11 @@
       <c r="AG96" s="3">
         <v>-13000</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-13000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,289 +8739,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-34000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-43000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-78000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-185000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-204000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-77000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-64000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-291000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-85000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-53000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-30000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-316000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-872000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-808000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-67000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-38000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-43000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-64000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-255000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-52000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>672000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-42000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-12000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>2000</v>
       </c>
       <c r="W101" s="3">
         <v>2000</v>
       </c>
       <c r="X101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>3000</v>
       </c>
       <c r="AD101" s="3">
         <v>3000</v>
       </c>
       <c r="AE101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>50000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-59000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-70000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>57000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-140000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-216000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>62000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-62000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>64000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>144000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>110000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>144000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-160000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-54000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-267000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>177000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>138000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-175000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>ODP</t>
   </si>
@@ -656,439 +656,452 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44828</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44737</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44464</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44282</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44191</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1871000</v>
+        <v>1717000</v>
       </c>
       <c r="E8" s="3">
+        <v>1869000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1806000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2009000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1908000</v>
-      </c>
       <c r="H8" s="3">
-        <v>2108000</v>
+        <v>1907000</v>
       </c>
       <c r="I8" s="3">
         <v>2106000</v>
       </c>
       <c r="J8" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2172000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2034000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2178000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2042000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2179000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2070000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2174000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2085000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2347000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4440000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2725000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2508000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2782000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2588000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2769000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2670000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2887000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2628000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1375000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1461000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1410000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1535000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1493000</v>
       </c>
-      <c r="H9" s="3">
-        <v>1627000</v>
-      </c>
       <c r="I9" s="3">
+        <v>1625000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1660000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1686000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1603000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1694000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1610000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1675000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4955000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3511000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3426000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1800000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3486000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2096000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1937000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2115000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2003000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2128000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2068000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2201000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2032000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>410000</v>
+        <v>342000</v>
       </c>
       <c r="E10" s="3">
+        <v>408000</v>
+      </c>
+      <c r="F10" s="3">
         <v>396000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>474000</v>
       </c>
-      <c r="G10" s="3">
-        <v>415000</v>
-      </c>
       <c r="H10" s="3">
+        <v>414000</v>
+      </c>
+      <c r="I10" s="3">
         <v>481000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>446000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>486000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>431000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>484000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>432000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>504000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>547000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>954000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>629000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>571000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>667000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>585000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>641000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>602000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>686000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>596000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>667000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>654000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,8 +1136,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1235,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,8 +1336,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1328,97 +1348,100 @@
         <v>33000</v>
       </c>
       <c r="E14" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F14" s="3">
         <v>74000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>3000</v>
       </c>
       <c r="L14" s="3">
         <v>3000</v>
       </c>
       <c r="M14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N14" s="3">
         <v>16000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>38000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>20000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>34000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>242000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>28000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>27000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>85000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>43000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>74000</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>14000</v>
       </c>
       <c r="AA14" s="3">
         <v>14000</v>
       </c>
       <c r="AB14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC14" s="3">
         <v>17000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>35000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>21000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>20000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>48000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,204 +1574,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1853000</v>
+        <v>1717000</v>
       </c>
       <c r="E17" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1837000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1918000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1862000</v>
-      </c>
       <c r="H17" s="3">
-        <v>2013000</v>
+        <v>1847000</v>
       </c>
       <c r="I17" s="3">
+        <v>1994000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2051000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2088000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2006000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2102000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2011000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2075000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2040000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2105000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2065000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2245000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4568000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2645000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2434000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2674000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2603000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2745000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2661000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2782000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-31000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>91000</v>
       </c>
-      <c r="G18" s="3">
-        <v>46000</v>
-      </c>
       <c r="H18" s="3">
-        <v>95000</v>
+        <v>60000</v>
       </c>
       <c r="I18" s="3">
+        <v>112000</v>
+      </c>
+      <c r="J18" s="3">
         <v>55000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>84000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>76000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>31000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>104000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>30000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>69000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>102000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-128000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>80000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>74000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>108000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>105000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>48000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>77000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>55000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>105000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>41000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>124000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>58000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,76 +1813,77 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>6000</v>
       </c>
       <c r="G20" s="3">
         <v>6000</v>
       </c>
       <c r="H20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I20" s="3">
         <v>4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>2000</v>
       </c>
       <c r="R20" s="3">
         <v>2000</v>
       </c>
       <c r="S20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T20" s="3">
         <v>6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>7000</v>
       </c>
       <c r="W20" s="3">
         <v>7000</v>
       </c>
       <c r="X20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>8000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>11000</v>
       </c>
       <c r="Z20" s="3">
         <v>11000</v>
@@ -1858,131 +1892,137 @@
         <v>11000</v>
       </c>
       <c r="AB20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>7000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>8000</v>
       </c>
       <c r="AE20" s="3">
         <v>8000</v>
       </c>
       <c r="AF20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>10000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>50000</v>
+        <v>21000</v>
       </c>
       <c r="E21" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>125000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>94000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>146000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>89000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>122000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>66000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>113000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>73000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>128000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>78000</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>126000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>68000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>150000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>133000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="W21" s="3">
+        <v>167000</v>
+      </c>
+      <c r="X21" s="3">
+        <v>45000</v>
+      </c>
+      <c r="Y21" s="3">
         <v>81000</v>
       </c>
-      <c r="H21" s="3">
-        <v>129000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>89000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>122000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>66000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>113000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>73000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>128000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>78000</v>
-      </c>
-      <c r="P21" s="3">
-        <v>126000</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>68000</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="Z21" s="3">
+        <v>70000</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>160000</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>110000</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>131000</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>107000</v>
+      </c>
+      <c r="AE21" s="3">
         <v>150000</v>
       </c>
-      <c r="S21" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>133000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>145000</v>
-      </c>
-      <c r="V21" s="3">
-        <v>167000</v>
-      </c>
-      <c r="W21" s="3">
-        <v>45000</v>
-      </c>
-      <c r="X21" s="3">
-        <v>81000</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>70000</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>160000</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>110000</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>131000</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>107000</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>150000</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>88000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>174000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>104000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="E22" s="3">
         <v>5000</v>
@@ -1997,281 +2037,290 @@
         <v>5000</v>
       </c>
       <c r="I22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J22" s="3">
         <v>6000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>28000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>23000</v>
       </c>
       <c r="X22" s="3">
         <v>23000</v>
       </c>
       <c r="Y22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>30000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>31000</v>
       </c>
       <c r="AA22" s="3">
         <v>31000</v>
       </c>
       <c r="AB22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>29000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>13000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>13000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>17000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>17000</v>
+        <v>-4000</v>
       </c>
       <c r="E23" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-32000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>92000</v>
       </c>
-      <c r="G23" s="3">
-        <v>47000</v>
-      </c>
       <c r="H23" s="3">
-        <v>94000</v>
+        <v>60000</v>
       </c>
       <c r="I23" s="3">
+        <v>111000</v>
+      </c>
+      <c r="J23" s="3">
         <v>52000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>89000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>74000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>100000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>98000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-150000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>66000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>74000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>93000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>85000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>28000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>55000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>41000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>35000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>121000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>46000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>64000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>33000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>25000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>158000</v>
+      </c>
+      <c r="AE24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>16000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>8000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>19000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>27000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>10000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>64000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>21000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>19000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>33000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>25000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>158000</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>14000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>47000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,204 +2417,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>15000</v>
+        <v>-4000</v>
       </c>
       <c r="E26" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-37000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>70000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>84000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K26" s="3">
+        <v>67000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>55000</v>
+      </c>
+      <c r="N26" s="3">
+        <v>32000</v>
+      </c>
+      <c r="O26" s="3">
+        <v>73000</v>
+      </c>
+      <c r="P26" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>63000</v>
+      </c>
+      <c r="R26" s="3">
+        <v>31000</v>
+      </c>
+      <c r="S26" s="3">
         <v>34000</v>
       </c>
-      <c r="H26" s="3">
-        <v>72000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>36000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>67000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>20000</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="T26" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="U26" s="3">
+        <v>45000</v>
+      </c>
+      <c r="V26" s="3">
         <v>55000</v>
       </c>
-      <c r="M26" s="3">
-        <v>32000</v>
-      </c>
-      <c r="N26" s="3">
-        <v>73000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>20000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>63000</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>31000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>34000</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-128000</v>
-      </c>
-      <c r="T26" s="3">
-        <v>45000</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
+        <v>60000</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>33000</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-117000</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>98000</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>74000</v>
+      </c>
+      <c r="AH26" s="3">
         <v>55000</v>
       </c>
-      <c r="V26" s="3">
-        <v>60000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="X26" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>60000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>19000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>33000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-117000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>98000</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>21000</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>74000</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>55000</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>15000</v>
+        <v>-4000</v>
       </c>
       <c r="E27" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-37000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>70000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>84000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K27" s="3">
+        <v>67000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M27" s="3">
+        <v>55000</v>
+      </c>
+      <c r="N27" s="3">
+        <v>32000</v>
+      </c>
+      <c r="O27" s="3">
+        <v>73000</v>
+      </c>
+      <c r="P27" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>63000</v>
+      </c>
+      <c r="R27" s="3">
+        <v>31000</v>
+      </c>
+      <c r="S27" s="3">
         <v>34000</v>
       </c>
-      <c r="H27" s="3">
-        <v>72000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>36000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>67000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>20000</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="T27" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="U27" s="3">
+        <v>45000</v>
+      </c>
+      <c r="V27" s="3">
         <v>55000</v>
       </c>
-      <c r="M27" s="3">
-        <v>32000</v>
-      </c>
-      <c r="N27" s="3">
-        <v>73000</v>
-      </c>
-      <c r="O27" s="3">
-        <v>20000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>63000</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>31000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>34000</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-128000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>45000</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
+        <v>60000</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>33000</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-117000</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>98000</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>74000</v>
+      </c>
+      <c r="AH27" s="3">
         <v>55000</v>
       </c>
-      <c r="V27" s="3">
-        <v>60000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="X27" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>60000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>19000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>33000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-117000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>98000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>21000</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>74000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>55000</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,16 +2720,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2680,47 +2741,47 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="I29" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="J29" s="3">
         <v>-19000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>7000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-306000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>28000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-225000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-13000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>23000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-266000</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2737,31 +2798,34 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>8000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>65000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>6000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>84000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>174000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,76 +3023,79 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-6000</v>
       </c>
       <c r="G32" s="3">
         <v>-6000</v>
       </c>
       <c r="H32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-2000</v>
       </c>
       <c r="R32" s="3">
         <v>-2000</v>
       </c>
       <c r="S32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T32" s="3">
         <v>-6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-7000</v>
       </c>
       <c r="W32" s="3">
         <v>-7000</v>
       </c>
       <c r="X32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-11000</v>
       </c>
       <c r="Z32" s="3">
         <v>-11000</v>
@@ -3034,126 +3104,132 @@
         <v>-11000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AE32" s="3">
         <v>-8000</v>
       </c>
       <c r="AF32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>70000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34000</v>
       </c>
-      <c r="H33" s="3">
-        <v>72000</v>
-      </c>
       <c r="I33" s="3">
+        <v>73000</v>
+      </c>
+      <c r="J33" s="3">
         <v>17000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>67000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>55000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-274000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>101000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-205000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>53000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>57000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-394000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>45000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>55000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>60000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-24000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>60000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>16000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>41000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>86000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>27000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>158000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>229000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,209 +3326,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>70000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34000</v>
       </c>
-      <c r="H35" s="3">
-        <v>72000</v>
-      </c>
       <c r="I35" s="3">
+        <v>73000</v>
+      </c>
+      <c r="J35" s="3">
         <v>17000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>67000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>55000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-274000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>101000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-205000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>53000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>57000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-394000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>45000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>55000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>60000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-24000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>60000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>16000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>41000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>86000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>27000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>158000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>229000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44828</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44737</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44464</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44282</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44191</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,106 +3609,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E41" s="3">
         <v>282000</v>
       </c>
-      <c r="E41" s="3">
-        <v>392000</v>
-      </c>
       <c r="F41" s="3">
+        <v>381000</v>
+      </c>
+      <c r="G41" s="3">
         <v>384000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>335000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>343000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>403000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>473000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>417000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>557000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>514000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>753000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>691000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>753000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>729000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>743000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>762000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>842000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>698000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>588000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>444000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>604000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>658000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>925000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>747000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>737000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>622000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>788000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>763000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>744000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>763000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3719,400 +3809,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>469000</v>
+      </c>
+      <c r="E43" s="3">
         <v>470000</v>
       </c>
-      <c r="E43" s="3">
-        <v>491000</v>
-      </c>
       <c r="F43" s="3">
+        <v>489000</v>
+      </c>
+      <c r="G43" s="3">
         <v>547000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>521000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>529000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>544000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>601000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>577000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>586000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>511000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>499000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>699000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>704000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>457000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>678000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>698000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>850000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1642000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1744000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1732000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1780000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>885000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>950000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>905000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>942000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>931000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>693000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>652000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>688000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>687000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>778000</v>
+      </c>
+      <c r="E44" s="3">
         <v>733000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>765000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>782000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>836000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>793000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>828000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>890000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>968000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>866000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>859000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>841000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>957000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>929000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>916000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1000000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1005000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>929000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1032000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1025000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1113000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1065000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1023000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1122000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E45" s="3">
         <v>39000</v>
       </c>
-      <c r="E45" s="3">
-        <v>30000</v>
-      </c>
       <c r="F45" s="3">
+        <v>104000</v>
+      </c>
+      <c r="G45" s="3">
         <v>41000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>46000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>148000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>135000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>144000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>505000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>783000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>64000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>253000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>59000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>60000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>79000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>75000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>103000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>84000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>75000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>112000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>142000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>216000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>225000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>241000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>269000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>313000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>244000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1476000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1524000</v>
       </c>
-      <c r="E46" s="3">
-        <v>1678000</v>
-      </c>
       <c r="F46" s="3">
+        <v>1739000</v>
+      </c>
+      <c r="G46" s="3">
         <v>1754000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1738000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1813000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1910000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2108000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2011000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2053000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2389000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2876000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2411000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2444000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2355000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2480000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2525000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2700000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3447000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3460000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3389000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3502000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2683000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3010000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2916000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4129,47 +4234,47 @@
         <v>1000</v>
       </c>
       <c r="H47" s="3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I47" s="3">
         <v>2000</v>
       </c>
       <c r="J47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K47" s="3">
         <v>3000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>17000</v>
       </c>
-      <c r="T47" s="3" t="s">
+      <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
@@ -4180,233 +4285,242 @@
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
         <v>842000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>847000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>853000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>858000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>863000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>869000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>874000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>879000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>885000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1338000</v>
       </c>
-      <c r="E48" s="3">
-        <v>1342000</v>
-      </c>
       <c r="F48" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1303000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1240000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1230000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1226000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1365000</v>
       </c>
       <c r="L48" s="3">
         <v>1365000</v>
       </c>
       <c r="M48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="N48" s="3">
         <v>1413000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1440000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1586000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1649000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1811000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1884000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2019000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2092000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2073000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2106000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2128000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>763000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>744000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>722000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>713000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>725000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>627000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>580000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>601000</v>
       </c>
       <c r="AH48" s="3">
         <v>601000</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>601000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E49" s="3">
         <v>447000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>448000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>510000</v>
       </c>
       <c r="G49" s="3">
         <v>510000</v>
       </c>
       <c r="H49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="I49" s="3">
         <v>511000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>510000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>511000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>514000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>516000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>518000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>519000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>916000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>451000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>965000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>956000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1319000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1332000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1333000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1345000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1331000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1336000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1342000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1319000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>395000</v>
       </c>
       <c r="AF49" s="3">
         <v>395000</v>
       </c>
       <c r="AG49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>396000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,106 +4718,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E52" s="3">
         <v>425000</v>
       </c>
-      <c r="E52" s="3">
-        <v>417000</v>
-      </c>
       <c r="F52" s="3">
+        <v>419000</v>
+      </c>
+      <c r="G52" s="3">
         <v>412000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>472000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>485000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>501000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>552000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>580000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>590000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>537000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>506000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>452000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>464000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1144000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>475000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>483000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>416000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>440000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>477000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>513000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>510000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>542000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>529000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>549000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>561000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>565000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>651000</v>
       </c>
       <c r="AF52" s="3">
         <v>651000</v>
       </c>
       <c r="AG52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AH52" s="3">
         <v>685000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,106 +4920,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3653000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3735000</v>
       </c>
-      <c r="E54" s="3">
-        <v>3886000</v>
-      </c>
       <c r="F54" s="3">
+        <v>3887000</v>
+      </c>
+      <c r="G54" s="3">
         <v>3980000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3961000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4041000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4149000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4418000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4474000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4529000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4865000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5351000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5378000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5598000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5614000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5745000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5865000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6454000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7311000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7343000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7353000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7471000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6166000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6472000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6359000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,106 +5097,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>755000</v>
+        <v>779000</v>
       </c>
       <c r="E57" s="3">
         <v>755000</v>
       </c>
       <c r="F57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="G57" s="3">
         <v>818000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>864000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>903000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>821000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>853000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>917000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>975000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>950000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>863000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>979000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>959000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>857000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1038000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>991000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1006000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1026000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1037000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1089000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1098000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1110000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1085000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1066000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>969000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>892000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>889000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>873000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>835000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>893000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5074,7 +5208,7 @@
         <v>10000</v>
       </c>
       <c r="E58" s="3">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="F58" s="3">
         <v>9000</v>
@@ -5083,480 +5217,495 @@
         <v>9000</v>
       </c>
       <c r="H58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I58" s="3">
         <v>12000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>16000</v>
       </c>
       <c r="J58" s="3">
         <v>16000</v>
       </c>
       <c r="K58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="L58" s="3">
         <v>17000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>20000</v>
       </c>
       <c r="N58" s="3">
         <v>20000</v>
       </c>
       <c r="O58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="P58" s="3">
         <v>22000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>48000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>30000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>104000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>841000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>842000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>837000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>841000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>95000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>92000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>97000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>93000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>96000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>28000</v>
       </c>
       <c r="AF58" s="3">
         <v>28000</v>
       </c>
       <c r="AG58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AH58" s="3">
         <v>29000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E59" s="3">
         <v>859000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>929000</v>
       </c>
       <c r="F59" s="3">
         <v>933000</v>
       </c>
       <c r="G59" s="3">
+        <v>933000</v>
+      </c>
+      <c r="H59" s="3">
         <v>909000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>930000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1022000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1024000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>969000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>973000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1295000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1298000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1099000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1147000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1556000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1228000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1114000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1235000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1227000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1277000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1255000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1294000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>980000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1051000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>957000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>952000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>926000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>983000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1642000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1624000</v>
       </c>
-      <c r="E60" s="3">
-        <v>1693000</v>
-      </c>
       <c r="F60" s="3">
+        <v>1697000</v>
+      </c>
+      <c r="G60" s="3">
         <v>1760000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1782000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1845000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1859000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1893000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1903000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1966000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2265000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2181000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2100000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2129000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2093000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2287000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2135000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2345000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3094000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3156000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3181000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3233000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2185000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2228000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2120000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E61" s="3">
         <v>115000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>165000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>164000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>172000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>210000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>172000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>175000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>177000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>181000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>228000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>333000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>337000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>344000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>354000</v>
       </c>
       <c r="R61" s="3">
         <v>354000</v>
       </c>
       <c r="S61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="T61" s="3">
         <v>642000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>548000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>575000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>593000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>618000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>632000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1444000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1646000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1668000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>927000</v>
+        <v>945000</v>
       </c>
       <c r="E62" s="3">
         <v>927000</v>
       </c>
       <c r="F62" s="3">
+        <v>1047000</v>
+      </c>
+      <c r="G62" s="3">
         <v>901000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>846000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>838000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>831000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>851000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>881000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>890000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>934000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>975000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1100000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1165000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1287000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1309000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1371000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1426000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1469000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1467000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1472000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1500000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>411000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>401000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>415000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>421000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>427000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>451000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>476000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>490000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>501000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,106 +6004,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2760000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2666000</v>
       </c>
-      <c r="E66" s="3">
-        <v>2785000</v>
-      </c>
       <c r="F66" s="3">
+        <v>2786000</v>
+      </c>
+      <c r="G66" s="3">
         <v>2825000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2800000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2893000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2862000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2919000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2961000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3037000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3427000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3489000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3537000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3638000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3734000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3950000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4148000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4319000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5138000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5216000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5271000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5365000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4040000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4275000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,106 +6546,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-370000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-297000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-312000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-275000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-344000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-379000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-451000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-468000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-535000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-562000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-617000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-343000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-444000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-356000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-409000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-427000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-484000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-45000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-144000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-204000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-180000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-173000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-160000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-220000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,106 +6950,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>893000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1069000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1101000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1155000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1161000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1148000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1287000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1499000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1513000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1492000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1438000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1862000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1841000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1960000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1880000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1795000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1717000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2135000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2173000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2127000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2082000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2106000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2126000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2197000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,209 +7152,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44828</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44737</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44464</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44282</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44191</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>70000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34000</v>
       </c>
-      <c r="H81" s="3">
-        <v>72000</v>
-      </c>
       <c r="I81" s="3">
+        <v>73000</v>
+      </c>
+      <c r="J81" s="3">
         <v>17000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>67000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>55000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-274000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>101000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-205000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>53000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>57000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-394000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>45000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>55000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>60000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-24000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>60000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>16000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>41000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>86000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>27000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>158000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>229000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,49 +7398,50 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="3">
         <v>29000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>28000</v>
       </c>
       <c r="F83" s="3">
         <v>28000</v>
       </c>
       <c r="G83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="H83" s="3">
         <v>29000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>34000</v>
       </c>
       <c r="L83" s="3">
         <v>34000</v>
       </c>
       <c r="M83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="N83" s="3">
         <v>36000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>43000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>46000</v>
       </c>
       <c r="Q83" s="3">
         <v>46000</v>
@@ -7251,55 +7450,58 @@
         <v>46000</v>
       </c>
       <c r="S83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="T83" s="3">
         <v>97000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>49000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>50000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>52000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>53000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>49000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>47000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>51000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>43000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>37000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>39000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,106 +8002,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E89" s="3">
         <v>38000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>112000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>157000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>158000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>163000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-114000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>171000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>86000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>309000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>180000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>188000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>152000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>212000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-58000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>60000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>61000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>304000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>45000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>217000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>40000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>282000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>34000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>102000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>36000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,106 +8142,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-14000</v>
       </c>
       <c r="R91" s="3">
         <v>-14000</v>
       </c>
       <c r="S91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-40000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-32000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-45000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-37000</v>
       </c>
       <c r="AB91" s="3">
         <v>-37000</v>
       </c>
       <c r="AC91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>13000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>31000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,106 +8443,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>77000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>53000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>762000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>776000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>23000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-29000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-61000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-52000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-68000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>23000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,8 +8583,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8401,28 +8635,28 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-13000</v>
       </c>
       <c r="U96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="V96" s="3">
         <v>-14000</v>
       </c>
       <c r="W96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-13000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-14000</v>
       </c>
       <c r="AA96" s="3">
         <v>-14000</v>
@@ -8434,7 +8668,7 @@
         <v>-14000</v>
       </c>
       <c r="AD96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AE96" s="3">
         <v>-13000</v>
@@ -8448,8 +8682,11 @@
       <c r="AH96" s="3">
         <v>-13000</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-13000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,106 +8985,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-113000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-34000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-43000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-78000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-185000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-204000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-77000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-64000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-291000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-85000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-53000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-316000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-872000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-808000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-67000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-38000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-43000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-64000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-255000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-52000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>672000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8849,191 +9098,197 @@
         <v>-1000</v>
       </c>
       <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-12000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>2000</v>
       </c>
       <c r="X101" s="3">
         <v>2000</v>
       </c>
       <c r="Y101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>3000</v>
       </c>
       <c r="AE101" s="3">
         <v>3000</v>
       </c>
       <c r="AF101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-110000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-59000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-70000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-140000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-216000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>62000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-62000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>24000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-21000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>64000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>144000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>110000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>144000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-160000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-54000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-267000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>177000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>138000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-175000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>ODP</t>
   </si>
@@ -656,452 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44828</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44737</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44464</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44373</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44282</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44191</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1717000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1869000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1806000</v>
       </c>
-      <c r="G8" s="3">
-        <v>2009000</v>
-      </c>
       <c r="H8" s="3">
+        <v>2007000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1907000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2106000</v>
       </c>
       <c r="J8" s="3">
         <v>2106000</v>
       </c>
       <c r="K8" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="L8" s="3">
         <v>2172000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2034000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2178000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2042000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2179000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2070000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2174000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2085000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2347000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4440000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2725000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2508000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2782000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2588000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2769000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2670000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2887000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2628000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1416000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1375000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1461000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1410000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1535000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1493000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1625000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1660000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1686000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1603000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1694000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1610000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1675000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4955000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3511000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3426000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1800000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3486000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2096000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1937000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2115000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2003000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2128000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2068000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2201000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2032000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E10" s="3">
         <v>342000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>408000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>396000</v>
       </c>
-      <c r="G10" s="3">
-        <v>474000</v>
-      </c>
       <c r="H10" s="3">
+        <v>472000</v>
+      </c>
+      <c r="I10" s="3">
         <v>414000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>481000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>446000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>486000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>431000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>484000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>432000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>504000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>547000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>954000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>629000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>571000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>667000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>585000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>641000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>602000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>686000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>596000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>667000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>654000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1137,8 +1150,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1238,8 +1252,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,132 +1356,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E14" s="3">
         <v>33000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>26000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>74000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3000</v>
       </c>
       <c r="M14" s="3">
         <v>3000</v>
       </c>
       <c r="N14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O14" s="3">
         <v>16000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>38000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>20000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>34000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>242000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>28000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>17000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>85000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>43000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>74000</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>14000</v>
       </c>
       <c r="AB14" s="3">
         <v>14000</v>
       </c>
       <c r="AC14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AD14" s="3">
         <v>17000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>35000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>22000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>21000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>20000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>48000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1541,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1717000</v>
+        <v>1740000</v>
       </c>
       <c r="E17" s="3">
-        <v>1828000</v>
+        <v>1684000</v>
       </c>
       <c r="F17" s="3">
-        <v>1837000</v>
+        <v>1803000</v>
       </c>
       <c r="G17" s="3">
-        <v>1918000</v>
+        <v>1761000</v>
       </c>
       <c r="H17" s="3">
-        <v>1847000</v>
+        <v>1893000</v>
       </c>
       <c r="I17" s="3">
-        <v>1994000</v>
+        <v>1838000</v>
       </c>
       <c r="J17" s="3">
+        <v>1988000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2051000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2088000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2006000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2102000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2011000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2075000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2040000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2105000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2065000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2245000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4568000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2645000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2434000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2674000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2603000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2745000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2661000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2782000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="E18" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>66000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>45000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>114000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>69000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>118000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>55000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>84000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>28000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>76000</v>
+      </c>
+      <c r="O18" s="3">
+        <v>31000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>104000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>30000</v>
+      </c>
+      <c r="R18" s="3">
+        <v>69000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>20000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>102000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>80000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>74000</v>
+      </c>
+      <c r="X18" s="3">
+        <v>108000</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>105000</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>77000</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>55000</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>105000</v>
+      </c>
+      <c r="AG18" s="3">
         <v>41000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>91000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>60000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>112000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>55000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>84000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>28000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>76000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>31000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>104000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>30000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>69000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>20000</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="AH18" s="3">
+        <v>124000</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>102000</v>
       </c>
-      <c r="T18" s="3">
-        <v>-128000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>80000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>74000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>108000</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>24000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>9000</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>105000</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>48000</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>77000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>55000</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>105000</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>41000</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>124000</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>58000</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>102000</v>
-      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,79 +1847,80 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="L20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="N20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="P20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q20" s="3">
         <v>5000</v>
       </c>
-      <c r="I20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>2000</v>
       </c>
       <c r="S20" s="3">
         <v>2000</v>
       </c>
       <c r="T20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U20" s="3">
         <v>6000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>21000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>7000</v>
       </c>
       <c r="X20" s="3">
         <v>7000</v>
       </c>
       <c r="Y20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>8000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>11000</v>
       </c>
       <c r="AA20" s="3">
         <v>11000</v>
@@ -1895,134 +1929,140 @@
         <v>11000</v>
       </c>
       <c r="AC20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>8000</v>
       </c>
       <c r="AF20" s="3">
         <v>8000</v>
       </c>
       <c r="AG20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AH20" s="3">
         <v>10000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21000</v>
+        <v>62000</v>
       </c>
       <c r="E21" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>49000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>140000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>90000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>148000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>89000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>122000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>66000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>113000</v>
+      </c>
+      <c r="O21" s="3">
         <v>73000</v>
       </c>
-      <c r="F21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>125000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>94000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>146000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>89000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>122000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>66000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>113000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>73000</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>128000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>78000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>126000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>68000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>150000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-25000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>133000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>145000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>167000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>81000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>70000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>160000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>110000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>131000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>107000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>150000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>88000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>174000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>104000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E22" s="3">
         <v>5000</v>
@@ -2040,287 +2080,296 @@
         <v>5000</v>
       </c>
       <c r="J22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K22" s="3">
         <v>6000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>28000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>23000</v>
       </c>
       <c r="Y22" s="3">
         <v>23000</v>
       </c>
       <c r="Z22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>30000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>31000</v>
       </c>
       <c r="AB22" s="3">
         <v>31000</v>
       </c>
       <c r="AC22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>29000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>13000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>14000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>13000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>17000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32000</v>
       </c>
-      <c r="G23" s="3">
-        <v>92000</v>
-      </c>
       <c r="H23" s="3">
+        <v>109000</v>
+      </c>
+      <c r="I23" s="3">
         <v>60000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>111000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>52000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>89000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>74000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>100000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>29000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>73000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>98000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-150000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>66000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>74000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>93000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>85000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>55000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>41000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>35000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>121000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>46000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
         <v>8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>17000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="L24" s="3">
         <v>22000</v>
       </c>
-      <c r="H24" s="3">
-        <v>17000</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="M24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P24" s="3">
         <v>27000</v>
       </c>
-      <c r="J24" s="3">
-        <v>16000</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="Q24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>64000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>33000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>25000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AD24" s="3">
         <v>22000</v>
       </c>
-      <c r="L24" s="3">
-        <v>8000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>19000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>27000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>10000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>64000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>21000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>19000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>33000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>25000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>158000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>47000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-37000</v>
       </c>
-      <c r="G26" s="3">
-        <v>70000</v>
-      </c>
       <c r="H26" s="3">
+        <v>82000</v>
+      </c>
+      <c r="I26" s="3">
         <v>43000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>84000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>36000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>67000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>55000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>32000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>73000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>63000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>34000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-128000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>45000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>55000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>60000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>60000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>33000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-117000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>98000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>74000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>55000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4000</v>
+        <v>58000</v>
       </c>
       <c r="E27" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="H27" s="3">
+        <v>70000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>34000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>73000</v>
+      </c>
+      <c r="K27" s="3">
+        <v>36000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>67000</v>
+      </c>
+      <c r="M27" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N27" s="3">
+        <v>55000</v>
+      </c>
+      <c r="O27" s="3">
+        <v>32000</v>
+      </c>
+      <c r="P27" s="3">
+        <v>73000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>20000</v>
+      </c>
+      <c r="R27" s="3">
+        <v>63000</v>
+      </c>
+      <c r="S27" s="3">
         <v>31000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-37000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>70000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>43000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>84000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>36000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>67000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>20000</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="T27" s="3">
+        <v>34000</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="V27" s="3">
+        <v>45000</v>
+      </c>
+      <c r="W27" s="3">
         <v>55000</v>
       </c>
-      <c r="N27" s="3">
-        <v>32000</v>
-      </c>
-      <c r="O27" s="3">
-        <v>73000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>63000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>31000</v>
-      </c>
-      <c r="S27" s="3">
-        <v>34000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-128000</v>
-      </c>
-      <c r="U27" s="3">
-        <v>45000</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
+        <v>60000</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>33000</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>-117000</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>98000</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>74000</v>
+      </c>
+      <c r="AI27" s="3">
         <v>55000</v>
       </c>
-      <c r="W27" s="3">
-        <v>60000</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>60000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>19000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>33000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-117000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>98000</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>21000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>74000</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>55000</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,68 +2781,71 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-69000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-16000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I29" s="3">
         <v>-9000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-11000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-19000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>7000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-306000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>28000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-225000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-10000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-13000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>23000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-266000</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2801,31 +2862,34 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>8000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>65000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>6000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>84000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>174000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,79 +3093,82 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="L32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="N32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="P32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-5000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-2000</v>
       </c>
       <c r="S32" s="3">
         <v>-2000</v>
       </c>
       <c r="T32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="U32" s="3">
         <v>-6000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-7000</v>
       </c>
       <c r="X32" s="3">
         <v>-7000</v>
       </c>
       <c r="Y32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-11000</v>
       </c>
       <c r="AA32" s="3">
         <v>-11000</v>
@@ -3107,129 +3177,135 @@
         <v>-11000</v>
       </c>
       <c r="AC32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AF32" s="3">
         <v>-8000</v>
       </c>
       <c r="AG32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-73000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-37000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>70000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>73000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>67000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>55000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-274000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>101000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-205000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>53000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>57000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-394000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>45000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>55000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>60000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>60000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>16000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>41000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>86000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>27000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>158000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>229000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-73000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-37000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>70000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>73000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>67000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>55000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-274000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>101000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-205000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>53000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>57000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-394000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>45000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>55000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>60000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>60000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>16000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>41000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>86000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>27000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>158000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>229000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44828</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44737</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44464</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44373</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44282</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44191</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,109 +3696,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E41" s="3">
         <v>180000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>282000</v>
       </c>
-      <c r="F41" s="3">
-        <v>381000</v>
-      </c>
       <c r="G41" s="3">
+        <v>392000</v>
+      </c>
+      <c r="H41" s="3">
         <v>384000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>335000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>343000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>403000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>473000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>417000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>557000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>514000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>753000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>691000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>753000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>729000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>743000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>762000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>842000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>698000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>588000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>444000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>604000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>658000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>925000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>747000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>737000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>622000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>788000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>763000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>744000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>763000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,472 +3902,487 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E43" s="3">
         <v>469000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>470000</v>
       </c>
-      <c r="F43" s="3">
-        <v>489000</v>
-      </c>
       <c r="G43" s="3">
+        <v>491000</v>
+      </c>
+      <c r="H43" s="3">
         <v>547000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>521000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>529000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>544000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>601000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>577000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>586000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>511000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>499000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>699000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>704000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>457000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>678000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>698000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>850000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1642000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1744000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1732000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1780000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>885000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>950000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>905000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>942000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>931000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>693000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>652000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>688000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>687000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>760000</v>
+      </c>
+      <c r="E44" s="3">
         <v>778000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>733000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>765000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>782000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>836000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>793000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>828000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>890000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>968000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>866000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>859000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>841000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>957000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>929000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>916000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1000000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1005000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>929000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1032000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1025000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1113000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1034000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1065000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1023000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1122000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>110000</v>
+      </c>
+      <c r="K45" s="3">
+        <v>135000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>144000</v>
+      </c>
+      <c r="M45" s="3">
         <v>49000</v>
       </c>
-      <c r="E45" s="3">
-        <v>39000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>104000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>41000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>46000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>148000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>135000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>144000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>49000</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>505000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>783000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>64000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>253000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>59000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>60000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>79000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>75000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>103000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>84000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>75000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>112000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>142000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>216000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>225000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>241000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>269000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>313000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>244000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1538000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1476000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1524000</v>
       </c>
-      <c r="F46" s="3">
-        <v>1739000</v>
-      </c>
       <c r="G46" s="3">
+        <v>1678000</v>
+      </c>
+      <c r="H46" s="3">
         <v>1754000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1738000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1813000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1910000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2108000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2011000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2053000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2389000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2876000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2411000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2444000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2355000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2480000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2525000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2700000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3447000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3460000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3389000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3502000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2683000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3010000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2916000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>2000</v>
       </c>
-      <c r="J47" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>17000</v>
       </c>
-      <c r="U47" s="3" t="s">
+      <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
@@ -4288,239 +4393,248 @@
         <v>0</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
         <v>842000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>847000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>853000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>858000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>863000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>869000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>874000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>879000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>885000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1287000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1338000</v>
       </c>
-      <c r="F48" s="3">
-        <v>1280000</v>
-      </c>
       <c r="G48" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1303000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1240000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1230000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1226000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1365000</v>
       </c>
       <c r="M48" s="3">
         <v>1365000</v>
       </c>
       <c r="N48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="O48" s="3">
         <v>1413000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1440000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1586000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1642000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1649000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1811000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1884000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2019000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2092000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2073000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2106000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2128000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>763000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>744000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>722000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>713000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>725000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>627000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>580000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>601000</v>
       </c>
       <c r="AI48" s="3">
         <v>601000</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>601000</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>461000</v>
+      </c>
+      <c r="E49" s="3">
         <v>446000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>447000</v>
       </c>
-      <c r="F49" s="3">
-        <v>448000</v>
-      </c>
       <c r="G49" s="3">
-        <v>510000</v>
+        <v>629000</v>
       </c>
       <c r="H49" s="3">
         <v>510000</v>
       </c>
       <c r="I49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="J49" s="3">
         <v>511000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>510000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>511000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>514000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>516000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>518000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>519000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>916000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1034000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>451000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>965000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>956000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1319000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1332000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1333000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1345000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1331000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1336000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1342000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1319000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>395000</v>
       </c>
       <c r="AG49" s="3">
         <v>395000</v>
       </c>
       <c r="AH49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AI49" s="3">
         <v>396000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,109 +4838,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>430000</v>
+        <v>274000</v>
       </c>
       <c r="E52" s="3">
-        <v>425000</v>
+        <v>272000</v>
       </c>
       <c r="F52" s="3">
-        <v>419000</v>
+        <v>278000</v>
       </c>
       <c r="G52" s="3">
-        <v>412000</v>
+        <v>277000</v>
       </c>
       <c r="H52" s="3">
-        <v>472000</v>
+        <v>271000</v>
       </c>
       <c r="I52" s="3">
-        <v>485000</v>
+        <v>314000</v>
       </c>
       <c r="J52" s="3">
+        <v>320000</v>
+      </c>
+      <c r="K52" s="3">
         <v>501000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>552000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>580000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>590000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>537000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>506000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>452000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>464000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1144000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>475000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>483000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>416000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>440000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>477000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>513000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>510000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>542000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>529000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>549000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>561000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>565000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>651000</v>
       </c>
       <c r="AG52" s="3">
         <v>651000</v>
       </c>
       <c r="AH52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>685000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,109 +5046,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3691000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3653000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3735000</v>
       </c>
-      <c r="F54" s="3">
-        <v>3887000</v>
-      </c>
       <c r="G54" s="3">
+        <v>3886000</v>
+      </c>
+      <c r="H54" s="3">
         <v>3980000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3961000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4041000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4149000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4418000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4474000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4529000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4865000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5351000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5378000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5598000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5614000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5745000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5865000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6454000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7311000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7343000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7353000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7471000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6166000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6472000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6359000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,109 +5228,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>773000</v>
+      </c>
+      <c r="E57" s="3">
         <v>779000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>755000</v>
       </c>
       <c r="F57" s="3">
         <v>755000</v>
       </c>
       <c r="G57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="H57" s="3">
         <v>818000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>864000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>903000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>821000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>853000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>917000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>975000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>950000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>863000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>979000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>959000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>857000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1038000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>991000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1006000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1026000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1037000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1089000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1098000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1110000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1085000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1066000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>969000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>892000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>889000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>873000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>835000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>893000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5211,501 +5345,516 @@
         <v>10000</v>
       </c>
       <c r="F58" s="3">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="G58" s="3">
-        <v>9000</v>
+        <v>282000</v>
       </c>
       <c r="H58" s="3">
         <v>9000</v>
       </c>
       <c r="I58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J58" s="3">
         <v>12000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>16000</v>
       </c>
       <c r="K58" s="3">
         <v>16000</v>
       </c>
       <c r="L58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="M58" s="3">
         <v>17000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>20000</v>
       </c>
       <c r="O58" s="3">
         <v>20000</v>
       </c>
       <c r="P58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>22000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>48000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>30000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>104000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>841000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>842000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>837000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>841000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>95000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>92000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>97000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>93000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>96000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>28000</v>
       </c>
       <c r="AG58" s="3">
         <v>28000</v>
       </c>
       <c r="AH58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AI58" s="3">
         <v>29000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>853000</v>
+        <v>36000</v>
       </c>
       <c r="E59" s="3">
-        <v>859000</v>
+        <v>34000</v>
       </c>
       <c r="F59" s="3">
-        <v>933000</v>
+        <v>5000</v>
       </c>
       <c r="G59" s="3">
-        <v>933000</v>
+        <v>44000</v>
       </c>
       <c r="H59" s="3">
-        <v>909000</v>
+        <v>36000</v>
       </c>
       <c r="I59" s="3">
-        <v>930000</v>
+        <v>38000</v>
       </c>
       <c r="J59" s="3">
+        <v>47000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1022000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1024000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>969000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>973000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1295000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1298000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1099000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1147000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1556000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1228000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1114000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1235000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1227000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1277000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1255000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1294000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>980000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1051000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>957000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>952000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>926000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>983000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1667000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1642000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1624000</v>
       </c>
-      <c r="F60" s="3">
-        <v>1697000</v>
-      </c>
       <c r="G60" s="3">
+        <v>1693000</v>
+      </c>
+      <c r="H60" s="3">
         <v>1760000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1782000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1845000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1859000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1893000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1903000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1966000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2265000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2181000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2100000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2129000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2093000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2287000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2135000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2345000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3094000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3156000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3181000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3233000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2185000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2228000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2120000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>173000</v>
+        <v>1037000</v>
       </c>
       <c r="E61" s="3">
-        <v>115000</v>
+        <v>992000</v>
       </c>
       <c r="F61" s="3">
-        <v>165000</v>
+        <v>906000</v>
       </c>
       <c r="G61" s="3">
-        <v>164000</v>
+        <v>954000</v>
       </c>
       <c r="H61" s="3">
+        <v>931000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>880000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>909000</v>
+      </c>
+      <c r="K61" s="3">
         <v>172000</v>
       </c>
-      <c r="I61" s="3">
-        <v>210000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>172000</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>175000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>177000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>181000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>228000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>333000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>337000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>344000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>354000</v>
       </c>
       <c r="S61" s="3">
         <v>354000</v>
       </c>
       <c r="T61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="U61" s="3">
         <v>642000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>548000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>575000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>593000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>618000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>632000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1444000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1646000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1668000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>945000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>927000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1047000</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G62" s="3">
-        <v>901000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>846000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>838000</v>
-      </c>
-      <c r="J62" s="3">
+        <v>120000</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>831000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>851000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>881000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>890000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>934000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>975000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1100000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1165000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1287000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1309000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1371000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1426000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1469000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1467000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1472000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1500000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>411000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>401000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>415000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>421000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>427000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>451000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>476000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>490000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>501000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,109 +6162,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2835000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2760000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2666000</v>
       </c>
-      <c r="F66" s="3">
-        <v>2786000</v>
-      </c>
       <c r="G66" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="H66" s="3">
         <v>2825000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2800000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2893000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2862000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2919000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2961000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3037000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3427000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3489000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3537000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3638000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3734000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3950000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4148000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4319000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5138000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5216000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5271000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5365000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4040000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4275000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,109 +6720,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-370000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-297000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-312000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-275000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-344000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-379000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-451000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-468000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-535000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-562000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-617000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-343000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-444000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-356000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-409000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-427000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-484000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-45000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-144000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-204000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-180000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-173000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-160000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-220000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,109 +7136,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>856000</v>
+      </c>
+      <c r="E76" s="3">
         <v>893000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1069000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1101000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1155000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1161000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1148000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1287000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1499000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1513000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1492000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1438000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1862000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1841000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1960000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1880000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1795000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1717000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2135000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2173000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2127000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2082000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2106000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2126000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2197000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44828</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44737</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44464</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44373</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44282</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44191</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-73000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-37000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>70000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>73000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>67000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>55000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-274000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>101000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-205000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>53000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>57000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-394000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>45000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>55000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>60000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>60000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>16000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>41000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>86000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>27000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>158000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>229000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,52 +7597,53 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>20000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>29000</v>
+        <v>25000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="G83" s="3">
-        <v>28000</v>
+        <v>-16000</v>
       </c>
       <c r="H83" s="3">
-        <v>29000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>30000</v>
+        <v>32000</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K83" s="3">
         <v>31000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>34000</v>
       </c>
       <c r="M83" s="3">
         <v>34000</v>
       </c>
       <c r="N83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="O83" s="3">
         <v>36000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>46000</v>
       </c>
       <c r="R83" s="3">
         <v>46000</v>
@@ -7453,55 +7652,58 @@
         <v>46000</v>
       </c>
       <c r="T83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="U83" s="3">
         <v>97000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>49000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>50000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>52000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>53000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>49000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>44000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>37000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>39000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>40000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
+        <v>38000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>70000</v>
+      </c>
+      <c r="H89" s="3">
+        <v>113000</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
+        <v>157000</v>
+      </c>
+      <c r="K89" s="3">
+        <v>158000</v>
+      </c>
+      <c r="L89" s="3">
+        <v>163000</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="N89" s="3">
+        <v>30000</v>
+      </c>
+      <c r="O89" s="3">
+        <v>100000</v>
+      </c>
+      <c r="P89" s="3">
+        <v>171000</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-11000</v>
       </c>
-      <c r="E89" s="3">
-        <v>38000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>70000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>112000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>157000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>158000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>163000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-114000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>30000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>100000</v>
-      </c>
-      <c r="O89" s="3">
-        <v>171000</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>86000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>309000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>180000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>188000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>152000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>212000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>60000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>61000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>304000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>45000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>217000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>40000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>282000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>34000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>102000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>36000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="E91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-35000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-25000</v>
       </c>
-      <c r="H91" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-14000</v>
       </c>
       <c r="S91" s="3">
         <v>-14000</v>
       </c>
       <c r="T91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-40000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-32000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-45000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-37000</v>
       </c>
       <c r="AC91" s="3">
         <v>-37000</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>13000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>31000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="E94" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-34000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18000</v>
       </c>
-      <c r="H94" s="3">
-        <v>77000</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>-31000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>53000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-33000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>762000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>776000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>23000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-29000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-52000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-68000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>23000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,31 +8817,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8638,28 +8872,28 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-13000</v>
       </c>
       <c r="V96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="W96" s="3">
         <v>-14000</v>
       </c>
       <c r="X96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-14000</v>
       </c>
       <c r="AB96" s="3">
         <v>-14000</v>
@@ -8671,7 +8905,7 @@
         <v>-14000</v>
       </c>
       <c r="AE96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AF96" s="3">
         <v>-13000</v>
@@ -8685,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>-13000</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-13000</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,307 +9231,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-61000</v>
-      </c>
-      <c r="E100" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>-113000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-34000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-43000</v>
       </c>
-      <c r="H100" s="3">
-        <v>-78000</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>-185000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-204000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-77000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-64000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-291000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-85000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-30000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-316000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-872000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-808000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-67000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-38000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-43000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-64000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-255000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>672000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>2000</v>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G101" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+        <v>-5000</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J101" s="3">
         <v>1000</v>
       </c>
       <c r="K101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-12000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>2000</v>
       </c>
       <c r="Y101" s="3">
         <v>2000</v>
       </c>
       <c r="Z101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>3000</v>
       </c>
       <c r="AF101" s="3">
         <v>3000</v>
       </c>
       <c r="AG101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH101" s="3">
         <v>2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-92000</v>
+        <v>4000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-110000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8000</v>
       </c>
-      <c r="G102" s="3">
-        <v>50000</v>
-      </c>
       <c r="H102" s="3">
-        <v>-8000</v>
+        <v>51000</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-59000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-70000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>57000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-140000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-216000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>62000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-14000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>64000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>144000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>110000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>144000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-160000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-267000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>177000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>138000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>18000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-175000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>ODP</t>
   </si>
@@ -656,465 +656,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44828</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44737</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44464</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44282</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44191</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1623000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1780000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1717000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1869000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1806000</v>
-      </c>
       <c r="H8" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2007000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1907000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2106000</v>
       </c>
       <c r="K8" s="3">
         <v>2106000</v>
       </c>
       <c r="L8" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="M8" s="3">
         <v>2172000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2034000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2178000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2042000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2179000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2070000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2174000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2085000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2347000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4440000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2725000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2508000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2782000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2588000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2769000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2670000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2887000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2628000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1293000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1416000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1375000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1461000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1410000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1409000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1535000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1493000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1625000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1660000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1686000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1603000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1694000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1610000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1675000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4955000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3511000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3426000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1800000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3486000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2096000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1937000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2115000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2003000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2128000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2068000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2201000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2032000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E10" s="3">
         <v>364000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>342000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>408000</v>
       </c>
-      <c r="G10" s="3">
-        <v>396000</v>
-      </c>
       <c r="H10" s="3">
+        <v>394000</v>
+      </c>
+      <c r="I10" s="3">
         <v>472000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>414000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>481000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>446000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>486000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>431000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>484000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>432000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>504000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>547000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>954000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>629000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>571000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>667000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>585000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>641000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>602000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>686000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>596000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>667000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>654000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,8 +1163,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,8 +1268,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1359,139 +1375,145 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-61000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>33000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>26000</v>
       </c>
-      <c r="G14" s="3">
-        <v>74000</v>
-      </c>
       <c r="H14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="3">
         <v>4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>3000</v>
       </c>
       <c r="N14" s="3">
         <v>3000</v>
       </c>
       <c r="O14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P14" s="3">
         <v>16000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>18000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>38000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>20000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>34000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>242000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>28000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>17000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>27000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>85000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>43000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>74000</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>14000</v>
       </c>
       <c r="AC14" s="3">
         <v>14000</v>
       </c>
       <c r="AD14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AE14" s="3">
         <v>17000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>35000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>22000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>21000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>20000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>24000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29000</v>
       </c>
-      <c r="G15" s="3">
-        <v>5000</v>
-      </c>
       <c r="H15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I15" s="3">
         <v>25000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1567,8 +1589,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1627,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1740000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1684000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1803000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1761000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1893000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1838000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1988000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2051000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2088000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2006000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2102000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2011000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2075000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2040000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2105000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2065000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2245000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4568000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2645000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2434000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2674000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2603000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2745000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2661000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2782000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E18" s="3">
         <v>40000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66000</v>
       </c>
-      <c r="G18" s="3">
-        <v>45000</v>
-      </c>
       <c r="H18" s="3">
+        <v>59000</v>
+      </c>
+      <c r="I18" s="3">
         <v>114000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>69000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>118000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>55000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>84000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>76000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>104000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>30000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>69000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>102000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-128000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>80000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>74000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>108000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>105000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>48000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>77000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>55000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>105000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>41000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>124000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>58000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,8 +1880,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1857,73 +1890,73 @@
         <v>2000</v>
       </c>
       <c r="E20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1000</v>
       </c>
       <c r="I20" s="3">
         <v>-1000</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>11000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>2000</v>
       </c>
       <c r="T20" s="3">
         <v>2000</v>
       </c>
       <c r="U20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V20" s="3">
         <v>6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>21000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>7000</v>
       </c>
       <c r="Y20" s="3">
         <v>7000</v>
       </c>
       <c r="Z20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>8000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>11000</v>
       </c>
       <c r="AB20" s="3">
         <v>11000</v>
@@ -1932,140 +1965,146 @@
         <v>11000</v>
       </c>
       <c r="AD20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>8000</v>
       </c>
       <c r="AG20" s="3">
         <v>8000</v>
       </c>
       <c r="AH20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AI20" s="3">
         <v>10000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E21" s="3">
         <v>62000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>52000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>96000</v>
       </c>
-      <c r="G21" s="3">
-        <v>49000</v>
-      </c>
       <c r="H21" s="3">
+        <v>61000</v>
+      </c>
+      <c r="I21" s="3">
         <v>140000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>90000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>148000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>89000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>122000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>66000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>113000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>73000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>128000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>78000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>126000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>68000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>150000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-25000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>133000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>145000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>167000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>45000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>81000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>70000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>160000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>110000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>131000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>107000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>150000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>88000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>174000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="3">
         <v>6000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>5000</v>
       </c>
       <c r="F22" s="3">
         <v>5000</v>
@@ -2083,293 +2122,302 @@
         <v>5000</v>
       </c>
       <c r="K22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L22" s="3">
         <v>6000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>28000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>23000</v>
       </c>
       <c r="Z22" s="3">
         <v>23000</v>
       </c>
       <c r="AA22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>30000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>31000</v>
       </c>
       <c r="AC22" s="3">
         <v>31000</v>
       </c>
       <c r="AD22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>29000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>13000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>14000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>13000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E23" s="3">
         <v>95000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-32000</v>
-      </c>
       <c r="H23" s="3">
+        <v>50000</v>
+      </c>
+      <c r="I23" s="3">
         <v>109000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>60000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>111000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>52000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>89000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>74000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>100000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>29000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>73000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>98000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-150000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>66000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>74000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>93000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>85000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>55000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>41000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>35000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>121000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>27000</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8000</v>
       </c>
-      <c r="G24" s="3">
-        <v>5000</v>
-      </c>
       <c r="H24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I24" s="3">
         <v>27000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>27000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-17000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>64000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>21000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>19000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>33000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>25000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>22000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>158000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>47000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2520,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E26" s="3">
         <v>68000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-37000</v>
-      </c>
       <c r="H26" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I26" s="3">
         <v>82000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>43000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>84000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>67000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>55000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>73000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>63000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>34000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-128000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>45000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>55000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>60000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>60000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>33000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-117000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>98000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>74000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>58000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-73000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>70000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>73000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>67000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>55000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>73000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>63000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>34000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-128000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>45000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>55000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>60000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>60000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>33000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-117000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>98000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>21000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>74000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,71 +2841,74 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-10000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-69000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-16000</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="I29" s="3">
         <v>-12000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-9000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-11000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-19000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>7000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-306000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>28000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-225000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-10000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-13000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>23000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-266000</v>
       </c>
-      <c r="V29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2865,31 +2925,34 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>8000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>65000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>6000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>84000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>174000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3055,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,8 +3162,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3105,73 +3174,73 @@
         <v>-2000</v>
       </c>
       <c r="E32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1000</v>
       </c>
       <c r="I32" s="3">
         <v>1000</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-2000</v>
       </c>
       <c r="T32" s="3">
         <v>-2000</v>
       </c>
       <c r="U32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="V32" s="3">
         <v>-6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-7000</v>
       </c>
       <c r="Y32" s="3">
         <v>-7000</v>
       </c>
       <c r="Z32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-11000</v>
       </c>
       <c r="AB32" s="3">
         <v>-11000</v>
@@ -3180,132 +3249,138 @@
         <v>-11000</v>
       </c>
       <c r="AD32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AG32" s="3">
         <v>-8000</v>
       </c>
       <c r="AH32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>58000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-73000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>70000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>73000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>67000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>55000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-274000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>101000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-205000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>53000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>57000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-394000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>45000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>55000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>60000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>60000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>16000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>41000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>86000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>27000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>158000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>229000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3483,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>58000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-73000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>70000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>73000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>67000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>55000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-274000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>101000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-205000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>53000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>57000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-394000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>45000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>55000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>60000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>60000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>16000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>41000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>86000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>27000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>158000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>229000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44828</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44737</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44464</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44282</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44191</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3743,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,112 +3782,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E41" s="3">
         <v>181000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>282000</v>
       </c>
-      <c r="G41" s="3">
-        <v>392000</v>
-      </c>
       <c r="H41" s="3">
+        <v>381000</v>
+      </c>
+      <c r="I41" s="3">
         <v>384000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>335000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>343000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>403000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>473000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>417000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>557000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>514000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>753000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>691000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>753000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>729000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>743000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>762000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>842000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>698000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>588000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>444000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>604000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>658000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>925000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>747000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>737000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>622000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>788000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>763000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>744000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>763000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3905,424 +3994,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E43" s="3">
         <v>554000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>469000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>470000</v>
       </c>
-      <c r="G43" s="3">
-        <v>491000</v>
-      </c>
       <c r="H43" s="3">
+        <v>489000</v>
+      </c>
+      <c r="I43" s="3">
         <v>547000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>521000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>529000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>544000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>601000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>577000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>586000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>511000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>499000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>699000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>704000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>457000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>678000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>698000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>850000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1642000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1744000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1732000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1780000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>885000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>950000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>905000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>942000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>931000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>693000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>652000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>688000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>687000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>770000</v>
+      </c>
+      <c r="E44" s="3">
         <v>760000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>778000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>733000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>765000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>782000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>836000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>793000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>828000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>890000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>968000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>866000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>859000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>841000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>957000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>929000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>916000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1000000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1005000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>929000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1032000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1025000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1113000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1065000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1023000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1122000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
-        <v>6000</v>
-      </c>
       <c r="H45" s="3">
+        <v>80000</v>
+      </c>
+      <c r="I45" s="3">
         <v>9000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>110000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>135000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>144000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>49000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>505000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>783000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>64000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>58000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>253000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>59000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>60000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>79000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>75000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>103000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>84000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>75000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>112000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>142000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>216000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>225000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>241000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>269000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>313000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>244000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1438000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1538000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1476000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1524000</v>
       </c>
-      <c r="G46" s="3">
-        <v>1678000</v>
-      </c>
       <c r="H46" s="3">
+        <v>1739000</v>
+      </c>
+      <c r="I46" s="3">
         <v>1754000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1738000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1813000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1910000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2108000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2011000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2053000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2389000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2876000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2411000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2444000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2355000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2480000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2525000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2700000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3447000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3460000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3389000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3502000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2683000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3010000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2916000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4347,45 +4451,45 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>2000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>15000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>17000</v>
       </c>
-      <c r="V47" s="3" t="s">
+      <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
@@ -4396,245 +4500,254 @@
         <v>0</v>
       </c>
       <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
         <v>842000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>847000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>853000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>858000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>863000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>869000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>874000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>879000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>885000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1121000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1287000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1338000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1161000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1303000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1240000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1230000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1226000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1365000</v>
       </c>
       <c r="N48" s="3">
         <v>1365000</v>
       </c>
       <c r="O48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="P48" s="3">
         <v>1413000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1440000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1586000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1642000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1649000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1811000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1884000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2019000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2092000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2073000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2106000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2128000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>763000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>744000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>722000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>713000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>725000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>627000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>580000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>601000</v>
       </c>
       <c r="AJ48" s="3">
         <v>601000</v>
       </c>
+      <c r="AK48" s="3">
+        <v>601000</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>591000</v>
+      </c>
+      <c r="E49" s="3">
         <v>461000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>446000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>447000</v>
       </c>
-      <c r="G49" s="3">
-        <v>629000</v>
-      </c>
       <c r="H49" s="3">
-        <v>510000</v>
+        <v>567000</v>
       </c>
       <c r="I49" s="3">
         <v>510000</v>
       </c>
       <c r="J49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="K49" s="3">
         <v>511000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>510000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>511000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>514000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>516000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>518000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>519000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>916000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1034000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>451000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>965000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>956000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1319000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1332000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1333000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1345000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1331000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1336000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1342000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1319000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>395000</v>
       </c>
       <c r="AH49" s="3">
         <v>395000</v>
       </c>
       <c r="AI49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>396000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4850,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,112 +4957,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E52" s="3">
         <v>274000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>272000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>278000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>277000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>271000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>314000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>320000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>501000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>552000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>580000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>590000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>537000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>506000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>452000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>464000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1144000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>475000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>483000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>416000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>440000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>477000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>513000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>510000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>542000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>529000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>549000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>561000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>565000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>651000</v>
       </c>
       <c r="AH52" s="3">
         <v>651000</v>
       </c>
       <c r="AI52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>685000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,112 +5171,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3529000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3691000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3653000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3735000</v>
       </c>
-      <c r="G54" s="3">
-        <v>3886000</v>
-      </c>
       <c r="H54" s="3">
+        <v>3887000</v>
+      </c>
+      <c r="I54" s="3">
         <v>3980000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3961000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4041000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4149000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4418000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4474000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4529000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4865000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5351000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5378000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5598000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5614000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5745000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5865000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6454000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7311000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7343000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7353000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7471000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6166000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6472000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6359000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5319,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,117 +5358,121 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E57" s="3">
         <v>773000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>779000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>755000</v>
       </c>
       <c r="G57" s="3">
         <v>755000</v>
       </c>
       <c r="H57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="I57" s="3">
         <v>818000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>864000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>903000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>821000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>853000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>917000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>975000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>950000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>863000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>979000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>959000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>857000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1038000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>991000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1006000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1026000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1037000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1089000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1098000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1110000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1085000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1066000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>969000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>892000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>889000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>873000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>835000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>893000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10000</v>
+        <v>273000</v>
       </c>
       <c r="E58" s="3">
         <v>10000</v>
@@ -5348,414 +5481,426 @@
         <v>10000</v>
       </c>
       <c r="G58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H58" s="3">
         <v>282000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9000</v>
       </c>
       <c r="I58" s="3">
         <v>9000</v>
       </c>
       <c r="J58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K58" s="3">
         <v>12000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>16000</v>
       </c>
       <c r="L58" s="3">
         <v>16000</v>
       </c>
       <c r="M58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="N58" s="3">
         <v>17000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>20000</v>
       </c>
       <c r="P58" s="3">
         <v>20000</v>
       </c>
       <c r="Q58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="R58" s="3">
         <v>22000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>23000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>48000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>30000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>104000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>841000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>842000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>837000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>841000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>95000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>92000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>97000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>93000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>96000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>28000</v>
       </c>
       <c r="AH58" s="3">
         <v>28000</v>
       </c>
       <c r="AI58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E59" s="3">
         <v>36000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>34000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5000</v>
       </c>
-      <c r="G59" s="3">
-        <v>44000</v>
-      </c>
       <c r="H59" s="3">
+        <v>53000</v>
+      </c>
+      <c r="I59" s="3">
         <v>36000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>38000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1022000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1024000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>969000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>973000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1295000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1099000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1147000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1556000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1228000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1114000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1235000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1227000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1277000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1255000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1294000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>980000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1051000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>957000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>952000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>926000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>983000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1543000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1667000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1642000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1624000</v>
       </c>
-      <c r="G60" s="3">
-        <v>1693000</v>
-      </c>
       <c r="H60" s="3">
+        <v>1697000</v>
+      </c>
+      <c r="I60" s="3">
         <v>1760000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1782000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1845000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1859000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1893000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1903000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1966000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2265000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2181000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2100000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2129000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2093000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2287000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2135000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2345000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3094000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3156000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3181000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3233000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2185000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2228000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2120000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1049000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1037000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>992000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>906000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>954000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>931000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>880000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>909000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>172000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>175000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>177000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>181000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>228000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>333000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>337000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>344000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>354000</v>
       </c>
       <c r="T61" s="3">
         <v>354000</v>
       </c>
       <c r="U61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="V61" s="3">
         <v>642000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>548000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>575000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>593000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>618000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>632000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1444000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1646000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1668000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>112000</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -5763,11 +5908,11 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
-        <v>120000</v>
-      </c>
-      <c r="H62" s="3" t="s">
+      <c r="G62" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="H62" s="3">
+        <v>116000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
@@ -5775,86 +5920,89 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>831000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>851000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>881000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>890000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>934000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>975000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1100000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1165000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1287000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1309000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1371000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1426000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1469000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1467000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1472000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1500000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>411000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>401000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>415000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>421000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>427000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>451000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>476000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>490000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>501000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6105,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6212,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,112 +6319,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2722000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2835000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2760000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2666000</v>
       </c>
-      <c r="G66" s="3">
-        <v>2785000</v>
-      </c>
       <c r="H66" s="3">
+        <v>2786000</v>
+      </c>
+      <c r="I66" s="3">
         <v>2825000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2800000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2893000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2862000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2919000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2961000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3037000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3427000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3489000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3537000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3638000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3734000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3950000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4148000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4319000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5138000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5216000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5271000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5365000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4040000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4275000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6467,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6572,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6679,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6786,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,112 +6893,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-315000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-312000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-370000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-297000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-312000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-275000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-344000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-379000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-451000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-468000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-535000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-562000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-617000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-343000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-444000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-356000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-409000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-427000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-484000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-45000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-89000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-144000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-204000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-180000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-173000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-160000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-220000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7107,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7214,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,112 +7321,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>807000</v>
+      </c>
+      <c r="E76" s="3">
         <v>856000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>893000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1069000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1101000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1155000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1161000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1148000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1287000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1499000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1513000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1492000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1438000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1862000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1841000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1960000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1880000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1795000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1717000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2135000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2173000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2127000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2082000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2106000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2126000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2197000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7535,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44828</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44737</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44464</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44282</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44191</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>58000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-73000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>70000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>73000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>67000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>55000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-274000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>101000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-205000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>53000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>57000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-394000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>45000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>55000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>60000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>60000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>16000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>41000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>86000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>27000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>158000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>229000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,55 +7795,56 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-16000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32000</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>34000</v>
       </c>
       <c r="N83" s="3">
         <v>34000</v>
       </c>
       <c r="O83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="P83" s="3">
         <v>36000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>46000</v>
       </c>
       <c r="S83" s="3">
         <v>46000</v>
@@ -7655,55 +7853,58 @@
         <v>46000</v>
       </c>
       <c r="U83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="V83" s="3">
         <v>97000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>50000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>52000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>53000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>49000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>44000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>51000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>37000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>39000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>40000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8007,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8114,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8221,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8328,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8435,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E89" s="3">
         <v>75000</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38000</v>
       </c>
-      <c r="G89" s="3">
-        <v>70000</v>
-      </c>
       <c r="H89" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I89" s="3">
         <v>113000</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>157000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>158000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>163000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-114000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>30000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>171000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>86000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>309000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>180000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>188000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>152000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>212000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>60000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>61000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>304000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>45000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>217000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>40000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>282000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>34000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>102000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>36000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8583,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-29000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-20000</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-14000</v>
       </c>
       <c r="T91" s="3">
         <v>-14000</v>
       </c>
       <c r="U91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-40000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-45000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-37000</v>
       </c>
       <c r="AD91" s="3">
         <v>-37000</v>
       </c>
       <c r="AE91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>13000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>31000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8795,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +8902,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-32000</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18000</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>53000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-33000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>762000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>776000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>23000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-52000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-68000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>23000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9050,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8844,8 +9077,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8875,28 +9108,28 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-13000</v>
       </c>
       <c r="W96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="X96" s="3">
         <v>-14000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-14000</v>
       </c>
       <c r="AC96" s="3">
         <v>-14000</v>
@@ -8908,7 +9141,7 @@
         <v>-14000</v>
       </c>
       <c r="AF96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AG96" s="3">
         <v>-13000</v>
@@ -8922,8 +9155,11 @@
       <c r="AJ96" s="3">
         <v>-13000</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-13000</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9262,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9369,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,316 +9476,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-40000</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-113000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-34000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-43000</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-185000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-204000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-77000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-64000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-291000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-53000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-30000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-316000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-872000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-808000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-67000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-43000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-255000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>672000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1000</v>
       </c>
       <c r="K101" s="3">
         <v>1000</v>
       </c>
       <c r="L101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>2000</v>
       </c>
       <c r="Z101" s="3">
         <v>2000</v>
       </c>
       <c r="AA101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>3000</v>
       </c>
       <c r="AG101" s="3">
         <v>3000</v>
       </c>
       <c r="AH101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-110000</v>
       </c>
-      <c r="G102" s="3">
-        <v>8000</v>
-      </c>
       <c r="H102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I102" s="3">
         <v>51000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-59000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-70000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>57000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-140000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-216000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>62000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-62000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-14000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>64000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>144000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>110000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>144000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-160000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-54000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-267000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>177000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>138000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-175000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>ODP</t>
   </si>
@@ -656,477 +656,490 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44828</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44737</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44464</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44282</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44191</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1699000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1623000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1780000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1717000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1869000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1803000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2007000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1907000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2106000</v>
       </c>
       <c r="L8" s="3">
         <v>2106000</v>
       </c>
       <c r="M8" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="N8" s="3">
         <v>2172000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2034000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2178000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2042000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2179000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2070000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2174000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2085000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2347000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4440000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2725000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2508000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2782000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2588000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2769000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2670000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2887000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2628000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1339000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1293000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1416000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1375000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1461000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1409000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1535000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1493000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1625000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1660000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1686000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1603000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1694000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1610000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1675000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4955000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3511000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3426000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1800000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3486000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2096000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1937000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2115000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2003000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2128000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2068000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2201000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2032000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E10" s="3">
         <v>330000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>364000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>342000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>408000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>394000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>472000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>414000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>481000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>446000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>486000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>431000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>484000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>432000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>504000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>547000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>954000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>629000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>571000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>667000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>585000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>641000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>602000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>686000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>596000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>667000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>654000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1164,8 +1177,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1271,8 +1285,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1378,145 +1395,151 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E14" s="3">
         <v>66000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-61000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>26000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>3000</v>
       </c>
       <c r="O14" s="3">
         <v>3000</v>
       </c>
       <c r="P14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q14" s="3">
         <v>16000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>18000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>38000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>20000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>34000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>242000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>28000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>17000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>27000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>85000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>43000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>74000</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>14000</v>
       </c>
       <c r="AD14" s="3">
         <v>14000</v>
       </c>
       <c r="AE14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AF14" s="3">
         <v>17000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>35000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>22000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>21000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>48000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20000</v>
       </c>
-      <c r="G15" s="3">
-        <v>29000</v>
-      </c>
       <c r="H15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="I15" s="3">
         <v>3000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>30000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1592,8 +1615,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1628,222 +1654,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1647000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1534000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1740000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1684000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1803000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1744000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1893000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1838000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1988000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2051000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2088000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2006000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2102000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2011000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2075000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2040000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2105000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2065000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2245000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4568000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2645000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2434000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2674000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2603000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2745000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2661000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2782000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E18" s="3">
         <v>89000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>40000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33000</v>
       </c>
-      <c r="G18" s="3">
-        <v>66000</v>
-      </c>
       <c r="H18" s="3">
+        <v>67000</v>
+      </c>
+      <c r="I18" s="3">
         <v>59000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>114000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>69000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>118000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>55000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>84000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>76000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>31000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>104000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>30000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>69000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>102000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-128000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>80000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>74000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>108000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>105000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>48000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>77000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>55000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>105000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>41000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>124000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>58000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1881,85 +1914,86 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>2000</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
         <v>2000</v>
       </c>
       <c r="F20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>1000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1000</v>
       </c>
       <c r="J20" s="3">
         <v>-1000</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>11000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>2000</v>
       </c>
       <c r="U20" s="3">
         <v>2000</v>
       </c>
       <c r="V20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W20" s="3">
         <v>6000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>21000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>7000</v>
       </c>
       <c r="Z20" s="3">
         <v>7000</v>
       </c>
       <c r="AA20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>8000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>11000</v>
       </c>
       <c r="AC20" s="3">
         <v>11000</v>
@@ -1968,135 +2002,141 @@
         <v>11000</v>
       </c>
       <c r="AE20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>7000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>8000</v>
       </c>
       <c r="AH20" s="3">
         <v>8000</v>
       </c>
       <c r="AI20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E21" s="3">
         <v>91000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>62000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>52000</v>
       </c>
-      <c r="G21" s="3">
-        <v>96000</v>
-      </c>
       <c r="H21" s="3">
+        <v>92000</v>
+      </c>
+      <c r="I21" s="3">
         <v>61000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>140000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>90000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>148000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>89000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>122000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>66000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>113000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>73000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>128000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>78000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>126000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>68000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>150000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-25000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>133000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>145000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>167000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>45000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>81000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>70000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>160000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>110000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>131000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>107000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>150000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>88000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>174000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>104000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2104,10 +2144,10 @@
         <v>7000</v>
       </c>
       <c r="E22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F22" s="3">
         <v>6000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5000</v>
       </c>
       <c r="G22" s="3">
         <v>5000</v>
@@ -2125,299 +2165,308 @@
         <v>5000</v>
       </c>
       <c r="L22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>28000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>23000</v>
       </c>
       <c r="AA22" s="3">
         <v>23000</v>
       </c>
       <c r="AB22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>30000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>31000</v>
       </c>
       <c r="AD22" s="3">
         <v>31000</v>
       </c>
       <c r="AE22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>29000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>13000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>17000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E23" s="3">
         <v>16000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>95000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>39000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>109000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>60000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>111000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>52000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>89000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>28000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>74000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>29000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>100000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>29000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>98000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-150000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>66000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>74000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>93000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>85000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>55000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>41000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>35000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>121000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>46000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27000</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>27000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-17000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>64000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-22000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>19000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>33000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>25000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>22000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>158000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>14000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>47000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2523,222 +2572,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E26" s="3">
         <v>11000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>68000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>39000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>84000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>67000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>55000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>73000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>63000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>34000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-128000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>45000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>55000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>60000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>60000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>33000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-117000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>98000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>21000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>74000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>55000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>58000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>70000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>73000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>67000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>55000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>73000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>63000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>34000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-128000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>45000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>55000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>60000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>60000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>33000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-117000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>98000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>21000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>74000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>55000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,74 +2902,77 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-14000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-10000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-69000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-16000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-76000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-12000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-9000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-11000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-19000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>7000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-306000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>28000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-225000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-10000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-13000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>23000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-266000</v>
       </c>
-      <c r="W29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -2928,31 +2989,34 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>8000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>65000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>6000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>174000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,8 +3122,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3165,85 +3232,88 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-2000</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
         <v>-2000</v>
       </c>
       <c r="F32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1000</v>
       </c>
       <c r="J32" s="3">
         <v>1000</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-2000</v>
       </c>
       <c r="U32" s="3">
         <v>-2000</v>
       </c>
       <c r="V32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-6000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-7000</v>
       </c>
       <c r="Z32" s="3">
         <v>-7000</v>
       </c>
       <c r="AA32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-11000</v>
       </c>
       <c r="AC32" s="3">
         <v>-11000</v>
@@ -3252,135 +3322,141 @@
         <v>-11000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AH32" s="3">
         <v>-8000</v>
       </c>
       <c r="AI32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>58000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-37000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>70000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>73000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>67000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>55000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-274000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>101000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-205000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>53000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>57000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-394000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>45000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>55000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>60000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>60000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>41000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>86000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>27000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>229000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3486,227 +3562,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>58000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-37000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>70000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>73000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>67000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>55000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-274000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>101000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-205000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>53000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>57000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-394000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>45000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>55000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>60000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>60000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>41000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>86000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>27000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>229000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44828</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44737</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44464</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44282</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44191</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3744,8 +3829,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3783,115 +3869,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E41" s="3">
         <v>166000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>181000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>180000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>282000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>381000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>384000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>335000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>343000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>403000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>473000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>417000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>557000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>514000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>753000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>691000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>753000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>729000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>743000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>762000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>842000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>698000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>588000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>444000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>604000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>658000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>925000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>747000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>737000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>622000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>788000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>763000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>744000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>763000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3997,222 +4087,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E43" s="3">
         <v>470000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>554000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>469000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>470000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>489000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>547000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>521000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>529000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>544000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>601000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>577000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>586000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>511000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>499000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>699000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>704000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>457000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>678000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>698000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>850000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1642000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1744000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1732000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1780000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>885000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>950000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>905000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>942000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>931000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>693000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>652000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>688000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>687000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E44" s="3">
         <v>770000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>760000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>778000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>733000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>765000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>782000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>836000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>793000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>828000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>890000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>968000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>866000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>859000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>841000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>957000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>929000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>916000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1000000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1005000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>929000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1032000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1025000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1113000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1065000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1023000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1122000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4220,213 +4319,219 @@
         <v>6000</v>
       </c>
       <c r="E45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F45" s="3">
         <v>12000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>80000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>110000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>135000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>144000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>49000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>505000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>783000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>64000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>58000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>253000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>59000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>60000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>79000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>75000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>103000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>100000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>84000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>75000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>112000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>142000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>216000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>225000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>241000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>269000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>313000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>244000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1442000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1438000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1538000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1476000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1524000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1739000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1754000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1738000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1813000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1910000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2108000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2011000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2053000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2389000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2876000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2411000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2444000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2355000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2480000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2525000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2700000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3447000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3460000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3389000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3502000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2683000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3010000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2916000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4454,45 +4559,45 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>2000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>15000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>17000</v>
       </c>
-      <c r="W47" s="3" t="s">
+      <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
@@ -4503,251 +4608,260 @@
         <v>0</v>
       </c>
       <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>842000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>847000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>853000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>858000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>863000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>869000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>874000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>879000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>885000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1169000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1121000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1287000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1338000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1161000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1303000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1240000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1230000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1226000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>1365000</v>
       </c>
       <c r="O48" s="3">
         <v>1365000</v>
       </c>
       <c r="P48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1413000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1440000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1586000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1642000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1649000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1811000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1884000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2019000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2092000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2073000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2106000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2128000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>763000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>744000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>722000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>713000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>725000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>627000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>580000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>601000</v>
       </c>
       <c r="AK48" s="3">
         <v>601000</v>
       </c>
+      <c r="AL48" s="3">
+        <v>601000</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E49" s="3">
         <v>591000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>461000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>446000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>447000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>567000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>510000</v>
       </c>
       <c r="J49" s="3">
         <v>510000</v>
       </c>
       <c r="K49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="L49" s="3">
         <v>511000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>510000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>511000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>514000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>516000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>518000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>519000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>916000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1034000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>451000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>965000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>956000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1319000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1332000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1333000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1345000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1331000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1336000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1342000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>395000</v>
       </c>
       <c r="AI49" s="3">
         <v>395000</v>
       </c>
       <c r="AJ49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AK49" s="3">
         <v>396000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4853,8 +4967,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4960,8 +5077,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4969,106 +5089,109 @@
         <v>273000</v>
       </c>
       <c r="E52" s="3">
+        <v>273000</v>
+      </c>
+      <c r="F52" s="3">
         <v>274000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>272000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>278000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>277000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>271000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>314000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>320000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>501000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>552000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>580000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>590000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>537000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>506000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>452000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>464000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1144000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>475000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>483000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>416000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>440000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>477000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>513000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>510000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>542000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>529000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>549000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>561000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>565000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>651000</v>
       </c>
       <c r="AI52" s="3">
         <v>651000</v>
       </c>
       <c r="AJ52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AK52" s="3">
         <v>685000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5174,115 +5297,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3467000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3529000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3691000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3653000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3735000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3887000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3980000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3961000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4041000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4149000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4418000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4474000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4529000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4865000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5351000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5378000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5598000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5614000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5745000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5865000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6454000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7311000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7343000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7353000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7471000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6166000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6472000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6359000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5320,8 +5449,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5359,123 +5489,127 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>698000</v>
+      </c>
+      <c r="E57" s="3">
         <v>697000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>773000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>779000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>755000</v>
       </c>
       <c r="H57" s="3">
         <v>755000</v>
       </c>
       <c r="I57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="J57" s="3">
         <v>818000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>864000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>903000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>821000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>853000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>917000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>975000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>950000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>863000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>979000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>959000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>857000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1038000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>991000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1006000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1026000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1037000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1089000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1098000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1110000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1085000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1066000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>969000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>892000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>889000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>873000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>835000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>893000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E58" s="3">
         <v>273000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>10000</v>
       </c>
       <c r="F58" s="3">
         <v>10000</v>
@@ -5484,426 +5618,438 @@
         <v>10000</v>
       </c>
       <c r="H58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I58" s="3">
         <v>282000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9000</v>
       </c>
       <c r="J58" s="3">
         <v>9000</v>
       </c>
       <c r="K58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L58" s="3">
         <v>12000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>16000</v>
       </c>
       <c r="M58" s="3">
         <v>16000</v>
       </c>
       <c r="N58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="O58" s="3">
         <v>17000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>20000</v>
       </c>
       <c r="Q58" s="3">
         <v>20000</v>
       </c>
       <c r="R58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="S58" s="3">
         <v>22000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>48000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>104000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>841000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>842000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>837000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>841000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>95000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>92000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>97000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>93000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>96000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>28000</v>
       </c>
       <c r="AI58" s="3">
         <v>28000</v>
       </c>
       <c r="AJ58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AK58" s="3">
         <v>29000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E59" s="3">
         <v>35000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>53000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>36000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1022000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1024000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>969000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>973000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1295000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1298000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1099000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1147000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1556000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1228000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1114000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1235000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1227000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1277000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1255000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1294000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>980000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1051000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>957000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>952000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>926000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>983000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1541000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1543000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1667000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1642000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1624000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1697000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1760000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1782000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1845000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1859000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1893000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1903000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1966000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2265000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2181000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2100000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2129000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2093000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2287000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2135000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2345000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3094000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3156000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3181000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3233000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2185000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2228000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2120000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>989000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1049000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1037000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>992000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>906000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>954000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>931000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>880000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>909000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>172000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>175000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>177000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>181000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>228000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>333000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>337000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>344000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>354000</v>
       </c>
       <c r="U61" s="3">
         <v>354000</v>
       </c>
       <c r="V61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="W61" s="3">
         <v>642000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>548000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>575000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>593000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>618000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>632000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1444000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1646000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1668000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>112000</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>8</v>
@@ -5911,11 +6057,11 @@
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>116000</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
@@ -5923,86 +6069,89 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>831000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>851000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>881000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>890000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>934000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>975000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1100000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1165000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1287000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1309000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1371000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1426000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1469000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1467000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1472000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1500000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>411000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>401000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>415000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>421000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>427000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>451000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>476000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>490000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>501000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6108,8 +6257,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6215,8 +6367,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6322,115 +6477,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2683000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2722000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2835000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2760000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2666000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2786000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2825000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2800000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2893000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2862000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2919000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2961000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3037000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3427000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3489000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3537000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3638000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3734000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3950000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4148000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4319000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5138000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5216000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5271000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5365000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4040000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4275000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6468,8 +6629,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6575,8 +6737,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6682,8 +6847,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,8 +6957,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6896,115 +7067,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-344000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-315000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-312000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-370000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-297000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-312000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-275000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-344000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-379000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-451000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-468000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-535000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-562000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-617000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-343000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-444000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-356000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-409000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-427000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-484000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-45000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-89000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-144000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-204000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-180000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-173000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-160000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-220000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7110,8 +7287,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7217,8 +7397,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7324,115 +7507,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E76" s="3">
         <v>807000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>856000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>893000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1069000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1101000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1155000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1161000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1148000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1287000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1499000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1513000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1492000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1438000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1862000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1841000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1960000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1880000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1795000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1717000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2135000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2173000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2127000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2082000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2106000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2126000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2197000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7538,227 +7727,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44828</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44737</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44464</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44282</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44191</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>58000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-37000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>70000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>73000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>67000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>55000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-274000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>101000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-205000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>53000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>57000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-394000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>45000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>55000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>60000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>60000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>41000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>86000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>27000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>229000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7796,58 +7994,59 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-11000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25000</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-16000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32000</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>32000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>34000</v>
       </c>
       <c r="O83" s="3">
         <v>34000</v>
       </c>
       <c r="P83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>36000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>21000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>43000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>46000</v>
       </c>
       <c r="T83" s="3">
         <v>46000</v>
@@ -7856,55 +8055,58 @@
         <v>46000</v>
       </c>
       <c r="V83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="W83" s="3">
         <v>97000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>49000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>50000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>52000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>53000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>49000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>44000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>47000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>51000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>37000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>39000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>41000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8010,8 +8212,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8117,8 +8322,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8224,8 +8432,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8331,8 +8542,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8438,115 +8652,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E89" s="3">
         <v>28000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>75000</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>69000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>113000</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>157000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>158000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>163000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-114000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>171000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>86000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>309000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>180000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>188000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>152000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>212000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>60000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>61000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>304000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>45000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>217000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>282000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>34000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>102000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>36000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8584,115 +8804,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22000</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>-35000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20000</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-14000</v>
       </c>
       <c r="U91" s="3">
         <v>-14000</v>
       </c>
       <c r="V91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-40000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-45000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-37000</v>
       </c>
       <c r="AE91" s="3">
         <v>-37000</v>
       </c>
       <c r="AF91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>13000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>31000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8798,8 +9022,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8905,115 +9132,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-41000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32000</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="G94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-34000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18000</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>53000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-33000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-16000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>762000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>776000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>23000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-68000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>23000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9051,8 +9284,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,8 +9314,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9111,28 +9345,28 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>-13000</v>
       </c>
       <c r="X96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="Y96" s="3">
         <v>-14000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-14000</v>
       </c>
       <c r="AD96" s="3">
         <v>-14000</v>
@@ -9144,7 +9378,7 @@
         <v>-14000</v>
       </c>
       <c r="AG96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AH96" s="3">
         <v>-13000</v>
@@ -9158,8 +9392,11 @@
       <c r="AK96" s="3">
         <v>-13000</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-13000</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9265,8 +9502,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9372,8 +9612,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9479,325 +9722,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-40000</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="G100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-113000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-34000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-43000</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-185000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-204000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-77000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-64000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-291000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-85000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-53000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-30000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-316000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-872000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-808000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-43000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-255000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>672000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="K101" s="3">
-        <v>1000</v>
       </c>
       <c r="L101" s="3">
         <v>1000</v>
       </c>
       <c r="M101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-12000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>2000</v>
       </c>
       <c r="AA101" s="3">
         <v>2000</v>
       </c>
       <c r="AB101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>3000</v>
       </c>
       <c r="AH101" s="3">
         <v>3000</v>
       </c>
       <c r="AI101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-110000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>51000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-59000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-70000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>57000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-140000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-216000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>62000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-62000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-21000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>64000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>144000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>110000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>144000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-160000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-54000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-267000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>177000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>138000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>18000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-175000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ODP_QTR_FIN.xlsx
@@ -656,490 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44828</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44737</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44464</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44282</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44191</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1586000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1699000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1623000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1780000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1717000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1869000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1803000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2007000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1907000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2106000</v>
       </c>
       <c r="M8" s="3">
         <v>2106000</v>
       </c>
       <c r="N8" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="O8" s="3">
         <v>2172000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2034000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2178000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2042000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2179000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2070000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2174000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2085000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2347000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4440000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2725000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2508000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2782000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2588000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2769000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2670000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2887000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2628000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2830000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2581000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2620000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2363000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2676000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2726000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2836000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1339000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1293000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1416000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1375000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1461000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1409000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1535000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1493000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1625000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1660000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1686000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1603000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1694000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1610000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1675000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4955000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3511000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3426000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1800000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3486000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2096000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1937000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2115000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2003000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2128000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2068000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2201000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2032000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2163000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3948000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3974000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3636000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4002000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2072000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2110000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E10" s="3">
         <v>360000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>330000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>364000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>342000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>408000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>394000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>472000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>414000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>481000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>446000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>486000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>431000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>484000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>432000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>504000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-2885000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1337000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1341000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>547000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>954000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>629000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>571000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>667000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>585000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>641000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>602000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>686000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>596000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>667000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-1367000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-1354000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-1273000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>654000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>726000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,8 +1191,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1288,8 +1302,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1398,151 +1415,157 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E14" s="3">
         <v>86000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>66000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-61000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>33000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>26000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>3000</v>
       </c>
       <c r="P14" s="3">
         <v>3000</v>
       </c>
       <c r="Q14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R14" s="3">
         <v>16000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>18000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>38000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>20000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>34000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>242000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>28000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>17000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>27000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>85000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>43000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>74000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>14000</v>
       </c>
       <c r="AE14" s="3">
         <v>14000</v>
       </c>
       <c r="AF14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>17000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>35000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>22000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>20000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>48000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E15" s="3">
         <v>27000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L15" s="3">
         <v>20000</v>
       </c>
-      <c r="H15" s="3">
-        <v>25000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>25000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>20000</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>30000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1618,8 +1641,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1655,228 +1681,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1561000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1647000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1534000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1740000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1684000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1802000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1744000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1893000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1838000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1988000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2051000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2088000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2006000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2102000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2011000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2075000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2040000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2105000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2065000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2245000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4568000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2645000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2434000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2674000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2603000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2745000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2661000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2782000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2753000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2526000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2515000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2322000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2552000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2668000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E18" s="3">
         <v>52000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>89000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>40000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>33000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>67000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>59000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>114000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>69000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>118000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>84000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>76000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>104000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>30000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>69000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>102000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-128000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>80000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>74000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>108000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>105000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>48000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>77000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>55000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>105000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>41000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>124000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>58000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1915,88 +1948,89 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2000</v>
       </c>
       <c r="F20" s="3">
         <v>2000</v>
       </c>
       <c r="G20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1000</v>
       </c>
       <c r="K20" s="3">
         <v>-1000</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>2000</v>
       </c>
       <c r="V20" s="3">
         <v>2000</v>
       </c>
       <c r="W20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X20" s="3">
         <v>6000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>21000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>7000</v>
       </c>
       <c r="AA20" s="3">
         <v>7000</v>
       </c>
       <c r="AB20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>8000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>11000</v>
       </c>
       <c r="AD20" s="3">
         <v>11000</v>
@@ -2005,152 +2039,158 @@
         <v>11000</v>
       </c>
       <c r="AF20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>7000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>8000</v>
       </c>
       <c r="AI20" s="3">
         <v>8000</v>
       </c>
       <c r="AJ20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AK20" s="3">
         <v>10000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="3">
         <v>79000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>91000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>62000</v>
       </c>
-      <c r="G21" s="3">
-        <v>52000</v>
-      </c>
       <c r="H21" s="3">
+        <v>56000</v>
+      </c>
+      <c r="I21" s="3">
         <v>92000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>61000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>140000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>90000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>148000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>89000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>122000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>66000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>113000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>73000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>128000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>78000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>126000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>68000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>150000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-25000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>133000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>145000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>167000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>45000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>81000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>70000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>160000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>110000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>131000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>107000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>150000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>174000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>104000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="E22" s="3">
         <v>7000</v>
       </c>
       <c r="F22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G22" s="3">
         <v>6000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5000</v>
       </c>
       <c r="H22" s="3">
         <v>5000</v>
@@ -2168,305 +2208,314 @@
         <v>5000</v>
       </c>
       <c r="M22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N22" s="3">
         <v>6000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>28000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>23000</v>
       </c>
       <c r="AB22" s="3">
         <v>23000</v>
       </c>
       <c r="AC22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>30000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>31000</v>
       </c>
       <c r="AE22" s="3">
         <v>31000</v>
       </c>
       <c r="AF22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>29000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>13000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>13000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>17000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-39000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>95000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>39000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>109000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>111000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>52000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>89000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>28000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>74000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>29000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>100000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>29000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>73000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>98000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-150000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>66000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>74000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>93000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>85000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>55000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>41000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>121000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>46000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27000</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>27000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-17000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>64000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-22000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>19000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>33000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>25000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>22000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>158000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>47000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-240000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,228 +2624,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>68000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>39000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>82000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>43000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>84000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>67000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>55000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>32000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>73000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>63000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>34000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-128000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>45000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>55000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>60000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>60000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>19000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>33000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-117000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>98000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>74000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>55000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>58000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-73000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-37000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>70000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>67000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>55000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>32000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>73000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>63000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>31000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-128000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>45000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>55000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>60000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>60000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>19000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>33000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-117000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>98000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>74000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>55000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2905,8 +2963,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2914,68 +2975,68 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-14000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-10000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-69000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-16000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-76000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-12000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-9000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-11000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-19000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>7000</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-306000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>28000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-225000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-10000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-13000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>23000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-266000</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
@@ -2992,31 +3053,34 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>8000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>65000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>84000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>174000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3125,8 +3189,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3235,88 +3302,91 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2000</v>
       </c>
       <c r="F32" s="3">
         <v>-2000</v>
       </c>
       <c r="G32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1000</v>
       </c>
       <c r="K32" s="3">
         <v>1000</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-2000</v>
       </c>
       <c r="V32" s="3">
         <v>-2000</v>
       </c>
       <c r="W32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="X32" s="3">
         <v>-6000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-21000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-7000</v>
       </c>
       <c r="AA32" s="3">
         <v>-7000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-11000</v>
       </c>
       <c r="AD32" s="3">
         <v>-11000</v>
@@ -3325,138 +3395,144 @@
         <v>-11000</v>
       </c>
       <c r="AF32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-8000</v>
       </c>
       <c r="AI32" s="3">
         <v>-8000</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-37000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>70000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>67000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>55000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-274000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>101000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-205000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>53000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>57000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-394000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>45000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>55000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>60000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>60000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>16000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>41000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>86000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>158000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>229000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3565,233 +3641,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-37000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>70000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>67000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>55000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-274000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>101000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-205000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>53000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>57000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-394000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>45000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>55000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>60000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>60000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>16000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>41000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>86000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>158000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>229000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44828</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44737</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44464</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44282</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44191</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,8 +3915,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3870,118 +3956,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E41" s="3">
         <v>185000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>166000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>181000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>180000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>282000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>381000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>384000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>335000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>343000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>403000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>473000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>417000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>557000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>514000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>753000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>691000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>753000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>729000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>743000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>762000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>842000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>698000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>588000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>444000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>604000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>658000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>925000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>747000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>737000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>622000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>788000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>763000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>744000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>763000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>801000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4090,448 +4180,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E43" s="3">
         <v>472000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>470000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>554000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>469000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>470000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>489000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>547000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>521000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>529000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>544000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>601000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>577000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>586000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>511000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>499000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>699000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>704000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>457000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>678000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>698000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>850000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1642000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1744000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1732000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1780000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>885000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>950000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>905000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>942000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>931000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>693000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>652000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>688000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>687000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>718000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>745000</v>
+      </c>
+      <c r="E44" s="3">
         <v>750000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>770000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>760000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>778000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>733000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>765000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>782000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>836000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>793000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>828000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>890000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>968000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>866000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>859000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>841000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>957000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>929000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>916000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1000000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1005000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>929000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1032000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1025000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1113000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1065000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1023000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1122000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1033000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1110000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1228000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1179000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1279000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1216000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="E45" s="3">
         <v>6000</v>
       </c>
       <c r="F45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G45" s="3">
         <v>12000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>80000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>110000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>135000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>144000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>49000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>505000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>783000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>64000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>58000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>253000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>59000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>60000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>79000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>75000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>103000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>100000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>84000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>75000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>112000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>142000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>216000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>225000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>241000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>269000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>313000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>244000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>665000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1431000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1442000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1438000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1538000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1476000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1524000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1739000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1754000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1738000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1813000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1910000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2108000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2011000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2053000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2389000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2876000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2411000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2444000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2355000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2480000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2525000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2700000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3447000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3460000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3389000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3502000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2683000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3010000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2916000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2928000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2871000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2832000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2912000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2924000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2973000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3400000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4562,45 +4667,45 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>2000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>15000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>17000</v>
       </c>
-      <c r="X47" s="3" t="s">
+      <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
@@ -4611,147 +4716,153 @@
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>842000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>847000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>853000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>858000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>863000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>869000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>874000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>879000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>885000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>890000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1117000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1169000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1121000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1287000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1300000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1338000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1161000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1303000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1240000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1230000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1226000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1244000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>1365000</v>
       </c>
       <c r="P48" s="3">
         <v>1365000</v>
       </c>
       <c r="Q48" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="R48" s="3">
         <v>1413000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1440000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1586000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1642000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1649000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1811000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1884000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2019000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2092000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2073000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2106000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2128000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>763000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>744000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>722000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>713000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>725000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>627000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>580000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>586000</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>601000</v>
       </c>
       <c r="AL48" s="3">
         <v>601000</v>
       </c>
+      <c r="AM48" s="3">
+        <v>601000</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4759,109 +4870,112 @@
         <v>458000</v>
       </c>
       <c r="E49" s="3">
+        <v>458000</v>
+      </c>
+      <c r="F49" s="3">
         <v>591000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>461000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>446000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>447000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>567000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>510000</v>
       </c>
       <c r="K49" s="3">
         <v>510000</v>
       </c>
       <c r="L49" s="3">
+        <v>510000</v>
+      </c>
+      <c r="M49" s="3">
         <v>511000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>510000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>511000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>514000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>516000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>518000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>519000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>916000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1034000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>451000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>965000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>956000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1332000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1333000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1345000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1331000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1336000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1342000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1319000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1330000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1299000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>413000</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>395000</v>
       </c>
       <c r="AJ49" s="3">
         <v>395000</v>
       </c>
       <c r="AK49" s="3">
+        <v>395000</v>
+      </c>
+      <c r="AL49" s="3">
         <v>396000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4970,8 +5084,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5080,118 +5197,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>273000</v>
+        <v>265000</v>
       </c>
       <c r="E52" s="3">
         <v>273000</v>
       </c>
       <c r="F52" s="3">
+        <v>273000</v>
+      </c>
+      <c r="G52" s="3">
         <v>274000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>272000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>278000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>277000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>271000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>314000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>320000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>501000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>552000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>580000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>590000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>537000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>506000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>452000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>464000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1144000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>475000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>483000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>416000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>440000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>477000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>513000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>510000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>542000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>529000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>549000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>561000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>565000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>656000</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>651000</v>
       </c>
       <c r="AJ52" s="3">
         <v>651000</v>
       </c>
       <c r="AK52" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AL52" s="3">
         <v>685000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5300,118 +5423,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3401000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3467000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3529000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3691000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3653000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3735000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3887000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3980000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3961000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4041000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4149000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4418000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4474000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4529000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4865000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5351000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5378000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5598000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5614000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5745000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5865000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6454000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7311000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7343000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7353000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7471000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6166000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6472000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6359000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6390000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6323000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5397000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5412000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5435000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5540000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5881000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5450,8 +5579,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5490,129 +5620,133 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E57" s="3">
         <v>698000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>697000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>773000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>779000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>755000</v>
       </c>
       <c r="I57" s="3">
         <v>755000</v>
       </c>
       <c r="J57" s="3">
+        <v>755000</v>
+      </c>
+      <c r="K57" s="3">
         <v>818000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>864000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>903000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>821000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>853000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>917000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>975000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>950000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>863000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>979000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>959000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>857000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1038000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>991000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1006000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1026000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1037000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1089000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1098000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1110000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1085000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1066000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>969000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>892000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>889000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>873000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>835000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>893000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>886000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>273000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>10000</v>
       </c>
       <c r="G58" s="3">
         <v>10000</v>
@@ -5621,438 +5755,450 @@
         <v>10000</v>
       </c>
       <c r="I58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J58" s="3">
         <v>282000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>9000</v>
       </c>
       <c r="K58" s="3">
         <v>9000</v>
       </c>
       <c r="L58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="M58" s="3">
         <v>12000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>16000</v>
       </c>
       <c r="N58" s="3">
         <v>16000</v>
       </c>
       <c r="O58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="P58" s="3">
         <v>17000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>20000</v>
       </c>
       <c r="R58" s="3">
         <v>20000</v>
       </c>
       <c r="S58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="T58" s="3">
         <v>22000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>23000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>48000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>30000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>104000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>841000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>842000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>837000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>841000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>95000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>92000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>97000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>93000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>96000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17000</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>28000</v>
       </c>
       <c r="AJ58" s="3">
         <v>28000</v>
       </c>
       <c r="AK58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AL58" s="3">
         <v>29000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E59" s="3">
         <v>28000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>35000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>53000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>36000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1022000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1024000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>969000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>973000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1295000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1298000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1099000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1147000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1556000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1228000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1114000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1235000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1227000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1277000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1255000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1294000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>980000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1051000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>957000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1044000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1058000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>952000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>926000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>983000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1109000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1524000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1541000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1543000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1667000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1642000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1624000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1697000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1760000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1782000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1845000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1859000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1893000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1903000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1966000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2265000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2181000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2100000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2129000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2093000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2287000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2135000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2345000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3094000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3156000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3181000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3233000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2185000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2228000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2120000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2106000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2046000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1858000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1827000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1846000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2031000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2322000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>930000</v>
+      </c>
+      <c r="E61" s="3">
         <v>989000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1049000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1037000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>992000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>906000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>954000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>931000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>880000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>909000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>172000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>175000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>177000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>181000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>228000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>333000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>337000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>344000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>354000</v>
       </c>
       <c r="V61" s="3">
         <v>354000</v>
       </c>
       <c r="W61" s="3">
+        <v>354000</v>
+      </c>
+      <c r="X61" s="3">
         <v>642000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>548000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>575000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>593000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>618000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>632000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1444000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1646000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1668000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1688000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1712000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1046000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1134000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1145000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1156000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1163000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3">
         <v>112000</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
@@ -6060,11 +6206,11 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>116000</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
@@ -6072,86 +6218,89 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>831000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>851000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>881000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>890000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>934000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>975000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1100000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1165000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1287000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1309000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1371000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1426000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1469000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1467000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1472000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1500000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>411000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>401000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>415000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>421000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>427000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>451000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>476000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>490000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>501000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>547000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6260,8 +6409,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6522,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6480,118 +6635,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2605000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2683000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2722000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2835000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2760000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2666000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2786000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2825000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2800000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2893000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2862000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2919000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2961000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3037000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3427000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3489000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3537000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3638000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3734000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3950000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4148000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4319000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5138000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5216000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5271000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5365000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4040000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4275000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4233000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4203000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3355000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3437000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3481000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3688000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4032000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6630,8 +6791,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6740,8 +6902,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6850,8 +7015,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6960,8 +7128,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7070,8 +7241,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7079,109 +7253,112 @@
         <v>-344000</v>
       </c>
       <c r="E72" s="3">
+        <v>-344000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-315000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-312000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-370000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-297000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-312000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-275000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-344000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-379000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-451000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-468000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-535000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-562000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-617000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-343000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-444000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-356000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-409000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-427000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-484000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-45000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-144000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-204000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-180000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-173000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-160000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-220000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-236000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-273000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-221000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-314000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-338000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-453000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-682000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7290,8 +7467,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7400,8 +7580,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7510,118 +7693,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>796000</v>
+      </c>
+      <c r="E76" s="3">
         <v>784000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>807000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>856000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>893000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1069000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1101000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1155000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1161000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1148000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1287000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1499000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1513000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1492000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1438000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1862000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1841000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1960000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1880000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1795000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1717000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2135000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2173000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2127000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2082000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2106000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2126000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2197000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2156000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2157000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2120000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2042000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1975000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1954000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1852000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1849000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7730,233 +7919,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44828</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44737</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44464</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44282</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44191</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-37000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>70000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>67000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>55000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-274000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>101000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-205000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>53000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>57000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-394000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>45000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>55000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>60000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>60000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>16000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>41000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>86000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>158000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>229000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7995,61 +8193,62 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-11000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25000</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-16000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32000</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>34000</v>
       </c>
       <c r="P83" s="3">
         <v>34000</v>
       </c>
       <c r="Q83" s="3">
+        <v>34000</v>
+      </c>
+      <c r="R83" s="3">
         <v>36000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>21000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>43000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>46000</v>
       </c>
       <c r="U83" s="3">
         <v>46000</v>
@@ -8058,55 +8257,58 @@
         <v>46000</v>
       </c>
       <c r="W83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="X83" s="3">
         <v>97000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>49000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>52000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>53000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>49000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>44000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>47000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>37000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>40000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>41000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8215,8 +8417,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8325,8 +8530,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8435,8 +8643,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8545,8 +8756,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8655,118 +8869,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E89" s="3">
         <v>57000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>75000</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>38000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K89" s="3">
+        <v>113000</v>
+      </c>
+      <c r="L89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H89" s="3">
-        <v>38000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>69000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>113000</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>157000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>158000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>163000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-114000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>171000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>86000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>309000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>180000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>188000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>152000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>212000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>60000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>61000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>304000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>45000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>217000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>40000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>282000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>102000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>36000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8805,118 +9025,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22000</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
+      <c r="M91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-31000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="O91" s="3">
         <v>-25000</v>
       </c>
-      <c r="J91" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-14000</v>
       </c>
       <c r="V91" s="3">
         <v>-14000</v>
       </c>
       <c r="W91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-40000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-45000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-37000</v>
       </c>
       <c r="AF91" s="3">
         <v>-37000</v>
       </c>
       <c r="AG91" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>13000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>31000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9025,8 +9249,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9135,118 +9362,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32000</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="3">
-        <v>-34000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-30000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>53000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21000</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-33000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-16000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>762000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>776000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>23000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-68000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-93000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-24000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9285,8 +9518,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9317,8 +9551,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9348,28 +9582,28 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-13000</v>
       </c>
       <c r="Y96" s="3">
-        <v>-14000</v>
+        <v>-13000</v>
       </c>
       <c r="Z96" s="3">
         <v>-14000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-14000</v>
       </c>
       <c r="AE96" s="3">
         <v>-14000</v>
@@ -9381,7 +9615,7 @@
         <v>-14000</v>
       </c>
       <c r="AH96" s="3">
-        <v>-13000</v>
+        <v>-14000</v>
       </c>
       <c r="AI96" s="3">
         <v>-13000</v>
@@ -9395,8 +9629,11 @@
       <c r="AL96" s="3">
         <v>-13000</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-13000</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9505,8 +9742,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9615,8 +9855,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9725,118 +9968,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-40000</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H100" s="3">
-        <v>-113000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-34000</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-291000</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="T100" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="U100" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="V100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="W100" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="X100" s="3">
+        <v>-872000</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>-808000</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-43000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-185000</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-204000</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="AC100" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>-291000</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-85000</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-53000</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-30000</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-316000</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-872000</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-808000</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-67000</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AD100" s="3">
+        <v>-255000</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>672000</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>-43000</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-64000</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-255000</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-52000</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>-66000</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-41000</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>672000</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>-127000</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,215 +10093,221 @@
         <v>-1000</v>
       </c>
       <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1000</v>
       </c>
       <c r="M101" s="3">
         <v>1000</v>
       </c>
       <c r="N101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>2000</v>
       </c>
       <c r="AB101" s="3">
         <v>2000</v>
       </c>
       <c r="AC101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>3000</v>
       </c>
       <c r="AI101" s="3">
         <v>3000</v>
       </c>
       <c r="AJ101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AK101" s="3">
         <v>2000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-110000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>51000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-59000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-70000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>57000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-140000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-216000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>62000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-62000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-21000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>64000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>144000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>110000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>144000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-160000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-54000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-267000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>177000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>138000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-188000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-175000</v>
       </c>
     </row>
